--- a/public/Qadian_Master_Booth_Analysis_AAP_INC.xlsx
+++ b/public/Qadian_Master_Booth_Analysis_AAP_INC.xlsx
@@ -1372,8 +1372,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>Allowal</t>
+          <t>Alowal</t>
         </is>
       </c>
       <c r="C4" s="28" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>Allowal</t>
+          <t>Alowal</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>Kheh Tikha + Chakk Gharoye</t>
+          <t>Theh Tikha</t>
         </is>
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>ਖੇਹ ਤਿੱਖਾ + ਚੱਕ ਘਰੋਏ</t>
+          <t>ਥੇਹ ਤਿੱਖਾ</t>
         </is>
       </c>
       <c r="D8" s="38" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Chakk Deepewal + Devidaspur</t>
+          <t>Chak Dipewal</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਦੀਪੇਵਾਲ + ਦੇਵੀਦਾਸਪੁਰ</t>
+          <t>ਚੱਕ ਦੀਪੇਵਾਲ</t>
         </is>
       </c>
       <c r="D9" s="39" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Kalyanpur</t>
+          <t>Kalayanpur</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>ਕਲਿਆਨਪੁਰ</t>
+          <t>ਕਲਿਆਣਪੁਰ</t>
         </is>
       </c>
       <c r="D17" s="38" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>ਕਲਿਆਨਪੁਰ</t>
+          <t>ਕਲਿਆਣਪੁਰ</t>
         </is>
       </c>
       <c r="D18" s="38" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D19" s="39" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D20" s="39" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D21" s="39" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>Mahandev Kalan</t>
+          <t>Mahadev Kalan</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="B30" s="28" t="inlineStr">
         <is>
-          <t>Trija Nagar + Rania</t>
+          <t>Trija Nagar</t>
         </is>
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>ਤਰੀਜਾ ਨੰਗਰ + ਰਣੀਆ</t>
+          <t>ਤਰੀਜਾ ਨਗਰ</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="B32" s="28" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>ਰਣੀਆ</t>
+          <t>ਰਣੀਆਂ</t>
         </is>
       </c>
       <c r="D32" s="38" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Daddwan</t>
+          <t>Dadwan</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>Daddwan</t>
+          <t>Dadwan</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Ahmadabad</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="B59" s="34" t="inlineStr">
         <is>
-          <t>Sujanpur, Maali Samrai</t>
+          <t>Sujanpur</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>ਸੁਜਾਨਪੁਰ, ਮਾਲੀ ਸਮਰਾਏ</t>
+          <t>ਸੁਜਾਨਪੁਰ</t>
         </is>
       </c>
       <c r="D59" s="29" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Badoye</t>
+          <t>Baroya</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Faizulla Chak</t>
+          <t>Faij Ulla Chak</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>ਫੈਜੁੱਲਾ ਚੱਕ</t>
+          <t>ਫੈਜ਼ੁੱਲਾ ਚੱਕ</t>
         </is>
       </c>
       <c r="D72" s="40" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>Faizulla Chak</t>
+          <t>Faij Ulla Chak</t>
         </is>
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>ਫੈਜੁੱਲਾ ਚੱਕ</t>
+          <t>ਫੈਜ਼ੁੱਲਾ ਚੱਕ</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>ਡੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
+          <t>ਦੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="C75" s="34" t="inlineStr">
         <is>
-          <t>ਡੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
+          <t>ਦੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>Khan Mallak</t>
+          <t>Khan Malak</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>ਖਾਨ ਮੱਲਕ</t>
+          <t>ਖਾਨ ਮਲਕ</t>
         </is>
       </c>
       <c r="D76" s="39" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="B77" s="34" t="inlineStr">
         <is>
-          <t>Pasnawal</t>
+          <t>Pasnawala</t>
         </is>
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
-          <t>ਪਸਨਾਵਾਲ</t>
+          <t>ਪਸਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D77" s="39" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>Pasnawal</t>
+          <t>Pasnawala</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>ਪਸਨਾਵਾਲ</t>
+          <t>ਪਸਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D78" s="41" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C81" s="34" t="inlineStr">
         <is>
-          <t>ਗਿਲ ਮੰਝ</t>
+          <t>ਗਿੱਲ ਮੰਜ</t>
         </is>
       </c>
       <c r="D81" s="38" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>ਛੀਨਾ ਰੇਤ ਵਾਲਾ</t>
+          <t>ਛੀਨਾ ਰੇਤਵਾਲਾ</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="B83" s="34" t="inlineStr">
         <is>
-          <t>Thakkar Sandhu</t>
+          <t>Thakar Sandhu</t>
         </is>
       </c>
       <c r="C83" s="34" t="inlineStr">
         <is>
-          <t>ਠੱਕਰ ਸੰਧੂ</t>
+          <t>ਠਾਕਰ ਸੰਧੂ</t>
         </is>
       </c>
       <c r="D83" s="39" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>Jogi Cheema + Chamiyari</t>
+          <t>Jogi Cheema</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>ਜੋਗੀ ਚੀਮਾ + ਚਮਿਆਰੀ</t>
+          <t>ਜੋਗੀ ਚੀਮਾ</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>Balaggan</t>
+          <t>Balagan</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
         <is>
-          <t>ਬਲੱਗਣ</t>
+          <t>ਬਲਾਗਣ</t>
         </is>
       </c>
       <c r="D88" s="39" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="B91" s="34" t="inlineStr">
         <is>
-          <t>Duluana</t>
+          <t>Duluaana</t>
         </is>
       </c>
       <c r="C91" s="34" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>Sahaipur, Langarkot, Haveli Harni</t>
+          <t>Sahaipur</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>ਸਹਾਈਪੁਰ, ਲੰਗਰਕੋਟ, ਹਵੇਲੀ ਹਾਰਨੀ</t>
+          <t>ਸਹਾਈਪੁਰ</t>
         </is>
       </c>
       <c r="D92" s="29" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="B93" s="34" t="inlineStr">
         <is>
-          <t>Bhikari Harni, Saidpur Harni, Bhore Harni</t>
+          <t>Bhikhari Harni</t>
         </is>
       </c>
       <c r="C93" s="34" t="inlineStr">
         <is>
-          <t>ਭਿਖਾਰੀ ਹਾਰਨੀ, ਸੈਦਪੁਰ ਹਾਰਨੀ, ਭੋਰੇ ਹਾਰਨੀ</t>
+          <t>ਭਿਖਾਰੀ ਹਾਰਨੀ</t>
         </is>
       </c>
       <c r="D93" s="39" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>Chhorian Bangar</t>
+          <t>Chhaurian Bangar</t>
         </is>
       </c>
       <c r="C104" s="28" t="inlineStr">
         <is>
-          <t>ਛੋੜੀਆ ਬਾਂਗਰ</t>
+          <t>ਛੌੜੀਆਂ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D104" s="29" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="B105" s="34" t="inlineStr">
         <is>
-          <t>Kotli Siania</t>
+          <t>Kotli Sainian</t>
         </is>
       </c>
       <c r="C105" s="34" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸਿਆਣੀਆਂ</t>
+          <t>ਕੋਟਲੀ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D105" s="41" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>Kotli Siania</t>
+          <t>Kotli Sainian</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸਿਆਣੀਆਂ</t>
+          <t>ਕੋਟਲੀ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D106" s="38" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>Saidowal Khurd, Bhaini Kaniya, Chakk Abdul</t>
+          <t>Bhaini Kanian</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
         <is>
-          <t>ਸੈਦੋਵਾਲ ਖੁਰਦ, ਭੈਣੀ ਕਾਨੀਆਂ, ਚੱਕ ਅਬਦੁਲ</t>
+          <t>ਭੈਣੀ ਕਾਨੀਆਂ</t>
         </is>
       </c>
       <c r="D108" s="38" t="inlineStr">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="B109" s="34" t="inlineStr">
         <is>
-          <t>Darapur, Jangal</t>
+          <t>Darapur</t>
         </is>
       </c>
       <c r="C109" s="34" t="inlineStr">
         <is>
-          <t>ਦਾਰਾਪੁਰ, ਜੰਗਲ</t>
+          <t>ਦਾਰਾਪੁਰ</t>
         </is>
       </c>
       <c r="D109" s="29" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>Gulepur, Gargarian</t>
+          <t>Gunopur</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
         <is>
-          <t>ਗੁਲੇਪੁਰ, ਗਾਰਗੜੀਆਂ</t>
+          <t>ਗੁਨੋਪੁਰ</t>
         </is>
       </c>
       <c r="D110" s="38" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="B111" s="34" t="inlineStr">
         <is>
-          <t>Gulepur</t>
+          <t>Gunopur</t>
         </is>
       </c>
       <c r="C111" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਲੇਪੁਰ</t>
+          <t>ਗੁਨੋਪੁਰ</t>
         </is>
       </c>
       <c r="D111" s="40" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="B113" s="34" t="inlineStr">
         <is>
-          <t>Jagowal Bet, Jaati Sarai, Bhuriya Gujran</t>
+          <t>Jagowal Bet</t>
         </is>
       </c>
       <c r="C113" s="34" t="inlineStr">
         <is>
-          <t>ਜਾਗੋਵਾਲ ਬੇਟ, ਜਾਤੀ ਸਰਾਏ, ਭੂਰੀਆ ਗੁਜਰਾਂ</t>
+          <t>ਜਾਗੋਵਾਲ ਬੇਟ</t>
         </is>
       </c>
       <c r="D113" s="39" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="B115" s="34" t="inlineStr">
         <is>
-          <t>Bhaini Paswal, Randhawa Colony</t>
+          <t>Bhaini Paswal</t>
         </is>
       </c>
       <c r="C115" s="34" t="inlineStr">
         <is>
-          <t>ਭੈਣੀ ਪਸਵਾਲ, ਰੰਧਾਵਾ ਕਲੋਨੀ</t>
+          <t>ਭੈਣੀ ਪਸਵਾਲ</t>
         </is>
       </c>
       <c r="D115" s="41" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="B116" s="28" t="inlineStr">
         <is>
-          <t>Kishanpur, Kathana, Yodhe</t>
+          <t>Kishanpur</t>
         </is>
       </c>
       <c r="C116" s="28" t="inlineStr">
         <is>
-          <t>ਕਿਸ਼ਨਪੁਰ, ਕਠਾਣਾ, ਯੋਧੇ</t>
+          <t>ਕਿਸ਼ਨਪੁਰ</t>
         </is>
       </c>
       <c r="D116" s="29" t="inlineStr">
@@ -7675,12 +7675,12 @@
       </c>
       <c r="B117" s="34" t="inlineStr">
         <is>
-          <t>Munan Kalan</t>
+          <t>Munnan Kalan</t>
         </is>
       </c>
       <c r="C117" s="34" t="inlineStr">
         <is>
-          <t>ਮੰਨਣ ਕਲਾਂ</t>
+          <t>ਮੁੰਨਣ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D117" s="29" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="B118" s="28" t="inlineStr">
         <is>
-          <t>Bujarh</t>
+          <t>Bajar</t>
         </is>
       </c>
       <c r="C118" s="28" t="inlineStr">
         <is>
-          <t>ਬੁਜਾੜ</t>
+          <t>ਬਾਜੜ</t>
         </is>
       </c>
       <c r="D118" s="29" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="B119" s="34" t="inlineStr">
         <is>
-          <t>Baruhia Molian, Piro Nangal, Sarwarpur, Bhulripur, Bhum</t>
+          <t>Bhurian Sainia</t>
         </is>
       </c>
       <c r="C119" s="34" t="inlineStr">
         <is>
-          <t>ਬਰੂਹੀਆ ਮੋਲੀਆਂ, ਪੀਰੋ ਨੰਗਲ, ਸਰਵਰਪੁਰ, ਭੁਲੜੀਪੁਰ, ਭੂਮ</t>
+          <t>ਭੂਰੀਆਂ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D119" s="39" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="C120" s="28" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਸਰੀਫ</t>
+          <t>ਚੱਕ ਸ਼ਰੀਫ</t>
         </is>
       </c>
       <c r="D120" s="29" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="C121" s="34" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਸਰੀਫ</t>
+          <t>ਚੱਕ ਸ਼ਰੀਫ</t>
         </is>
       </c>
       <c r="D121" s="29" t="inlineStr">
@@ -7945,12 +7945,12 @@
       </c>
       <c r="B122" s="28" t="inlineStr">
         <is>
-          <t>Kotla Gujran, Jhanda Gujran</t>
+          <t>Kotla Gujran</t>
         </is>
       </c>
       <c r="C122" s="28" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਗੁਜਰਾਂ, ਝੰਡਾ ਗੁਜਰਾਂ</t>
+          <t>ਕੋਟਲਾ ਗੁਜਰਾਂ</t>
         </is>
       </c>
       <c r="D122" s="39" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="B125" s="34" t="inlineStr">
         <is>
-          <t>Kotli Garhwan</t>
+          <t>Kotli Ralwan</t>
         </is>
       </c>
       <c r="C125" s="34" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਗਰਲਵਾਂ</t>
+          <t>ਕੋਟਲੀ ਰਲਵਾਂ</t>
         </is>
       </c>
       <c r="D125" s="39" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="B126" s="28" t="inlineStr">
         <is>
-          <t>Chak Yakub</t>
+          <t>Chak Yaqub</t>
         </is>
       </c>
       <c r="C126" s="28" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C127" s="34" t="inlineStr">
         <is>
-          <t>ਲਾਧੂਪੁਰ</t>
+          <t>ਲੱਧੂਪੁਰ</t>
         </is>
       </c>
       <c r="D127" s="41" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="C128" s="28" t="inlineStr">
         <is>
-          <t>ਨੈਨੇਕੋਟ</t>
+          <t>ਨੈਣੇਕੋਟ</t>
         </is>
       </c>
       <c r="D128" s="39" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="B130" s="28" t="inlineStr">
         <is>
-          <t>Raowal</t>
+          <t>Rauwal</t>
         </is>
       </c>
       <c r="C130" s="28" t="inlineStr">
         <is>
-          <t>ਰਾਓਵਾਲ</t>
+          <t>ਰਾਊਵਾਲ</t>
         </is>
       </c>
       <c r="D130" s="29" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C131" s="34" t="inlineStr">
         <is>
-          <t>ਨਿਮਾਣੇ</t>
+          <t>ਨੀਮਾਣੇ</t>
         </is>
       </c>
       <c r="D131" s="29" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="B133" s="34" t="inlineStr">
         <is>
-          <t>Bhittewadd</t>
+          <t>Bhite Wad</t>
         </is>
       </c>
       <c r="C133" s="34" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="B134" s="28" t="inlineStr">
         <is>
-          <t>Kot Todar Mal</t>
+          <t>Kot Todar Mall</t>
         </is>
       </c>
       <c r="C134" s="28" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="B135" s="34" t="inlineStr">
         <is>
-          <t>Kot Todar Mal</t>
+          <t>Kot Todar Mall</t>
         </is>
       </c>
       <c r="C135" s="34" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="B136" s="28" t="inlineStr">
         <is>
-          <t>Rooda Buttar</t>
+          <t>Rurha Buttar</t>
         </is>
       </c>
       <c r="C136" s="28" t="inlineStr">
         <is>
-          <t>ਰੂੜਾ ਬੁੱਟਰ</t>
+          <t>ਰੂੜ੍ਹਾ ਬੁੱਟਰ</t>
         </is>
       </c>
       <c r="D136" s="29" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B137" s="34" t="inlineStr">
         <is>
-          <t>Malian</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="C137" s="34" t="inlineStr">
         <is>
-          <t>ਮਾਲੀਆਂ</t>
+          <t>ਮਾਲੀਆ</t>
         </is>
       </c>
       <c r="D137" s="39" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="B140" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 4</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C140" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 4</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D140" s="38" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="B141" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 2</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C141" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 2</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D141" s="40" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="B142" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 2</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C142" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 2</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D142" s="39" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="B143" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 1</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C143" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 1</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D143" s="41" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="B144" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 7</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C144" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 7</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D144" s="38" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="B145" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 8</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C145" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 8</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D145" s="29" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="B146" s="28" t="inlineStr">
         <is>
-          <t>Qadian Civil Lines</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C146" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਸਿਵਲ ਲਾਈਨ</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D146" s="29" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="B147" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 6</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C147" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 6</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D147" s="39" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="B148" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 5</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C148" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 5</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D148" s="40" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="B149" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 5</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C149" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 5</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D149" s="39" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="B150" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 11</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C150" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 11</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D150" s="39" t="inlineStr">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="B151" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 10</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C151" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 10</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D151" s="29" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="B152" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 12</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C152" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 12</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D152" s="39" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="B153" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 9</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C153" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 9</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D153" s="40" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="B154" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 13</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C154" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 13</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D154" s="40" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="B155" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 15</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C155" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 15</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D155" s="40" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B156" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 14</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C156" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 14</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D156" s="39" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="B157" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 3</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C157" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 3</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D157" s="41" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="B159" s="34" t="inlineStr">
         <is>
-          <t>Bhagatpura Rathwala</t>
+          <t>Patti Bhagtupur</t>
         </is>
       </c>
       <c r="C159" s="34" t="inlineStr">
         <is>
-          <t>ਭਗਤਪੁਰਾ ਰੱਥਵਾਲਾ</t>
+          <t>ਪੱਤੀ ਭਗਤੂਪੁਰ</t>
         </is>
       </c>
       <c r="D159" s="38" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="B160" s="28" t="inlineStr">
         <is>
-          <t>Nangal Baghbana</t>
+          <t>Nangal Bagbana</t>
         </is>
       </c>
       <c r="C160" s="28" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਬਾਗਬਾਨਾ</t>
+          <t>ਨੰਗਲ ਬਾਗ਼ਬਾਨਾਂ</t>
         </is>
       </c>
       <c r="D160" s="29" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="B161" s="34" t="inlineStr">
         <is>
-          <t>Chhota Nangal</t>
+          <t>Chota Nangal</t>
         </is>
       </c>
       <c r="C161" s="34" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="B162" s="28" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C162" s="28" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="B163" s="34" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C163" s="34" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="B164" s="28" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C164" s="28" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="C165" s="34" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D165" s="39" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="C166" s="28" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D166" s="39" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="C167" s="34" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D167" s="40" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="B168" s="28" t="inlineStr">
         <is>
-          <t>Daili Bangar</t>
+          <t>Bhaini Bangar</t>
         </is>
       </c>
       <c r="C168" s="28" t="inlineStr">
         <is>
-          <t>ਡੈਲੀ ਬਾਂਗਰ</t>
+          <t>ਭੈਣੀ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D168" s="41" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B169" s="34" t="inlineStr">
         <is>
-          <t>Daili Bangar</t>
+          <t>Bhaini Banger</t>
         </is>
       </c>
       <c r="C169" s="34" t="inlineStr">
         <is>
-          <t>ਡੈਲੀ ਬਾਂਗਰ</t>
+          <t>ਭੈਣੀ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D169" s="41" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="B171" s="34" t="inlineStr">
         <is>
-          <t>Salarpur</t>
+          <t>Salahpur</t>
         </is>
       </c>
       <c r="C171" s="34" t="inlineStr">
         <is>
-          <t>ਸਲਾਰਪੁਰ</t>
+          <t>ਸਲਾਹਪੁਰ</t>
         </is>
       </c>
       <c r="D171" s="39" t="inlineStr">
@@ -10645,12 +10645,12 @@
       </c>
       <c r="B172" s="28" t="inlineStr">
         <is>
-          <t>Chandogi Mayian Singh</t>
+          <t>Pandori Maiya Singh</t>
         </is>
       </c>
       <c r="C172" s="28" t="inlineStr">
         <is>
-          <t>ਚੰਡੋਗੀ ਮਈਆਂ ਸਿੰਘ</t>
+          <t>ਪੰਡੋਰੀ ਮਈਆਂ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D172" s="39" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="C173" s="34" t="inlineStr">
         <is>
-          <t>ਕੂੰਟ</t>
+          <t>ਕੁੰਟ</t>
         </is>
       </c>
       <c r="D173" s="39" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="C174" s="28" t="inlineStr">
         <is>
-          <t>ਗੋਹਤ ਖੁਰਦ</t>
+          <t>ਘੋਟ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D174" s="39" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="B176" s="28" t="inlineStr">
         <is>
-          <t>Chib</t>
+          <t>Chibb</t>
         </is>
       </c>
       <c r="C176" s="28" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="C177" s="34" t="inlineStr">
         <is>
-          <t>ਭੱਟੀਆਂ</t>
+          <t>ਭੱਠੀਆਂ</t>
         </is>
       </c>
       <c r="D177" s="39" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="C178" s="28" t="inlineStr">
         <is>
-          <t>ਭੱਟੀਆਂ</t>
+          <t>ਭੱਠੀਆਂ</t>
         </is>
       </c>
       <c r="D178" s="29" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="B179" s="34" t="inlineStr">
         <is>
-          <t>Jangowal Bangar</t>
+          <t>Jagowal Bangar</t>
         </is>
       </c>
       <c r="C179" s="34" t="inlineStr">
         <is>
-          <t>ਜਾਂਗੋਵਾਲ ਬਾਂਗਰ</t>
+          <t>ਜਾਗੋਵਾਲ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D179" s="39" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="B180" s="28" t="inlineStr">
         <is>
-          <t>Kiri Afghana</t>
+          <t>Kiri Afgana</t>
         </is>
       </c>
       <c r="C180" s="28" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="B183" s="34" t="inlineStr">
         <is>
-          <t>Ghukkan</t>
+          <t>Ghookla</t>
         </is>
       </c>
       <c r="C183" s="34" t="inlineStr">
         <is>
-          <t>ਘੁੱਕਲਾਂ</t>
+          <t>ਘੂਕਲਾ</t>
         </is>
       </c>
       <c r="D183" s="40" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="B187" s="34" t="inlineStr">
         <is>
-          <t>Tugalwal</t>
+          <t>Tugalwala</t>
         </is>
       </c>
       <c r="C187" s="34" t="inlineStr">
         <is>
-          <t>ਤੁਗਲਵਾਲ</t>
+          <t>ਤੁਗਲਵਾਲਾ</t>
         </is>
       </c>
       <c r="D187" s="39" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B188" s="28" t="inlineStr">
         <is>
-          <t>Tugalwal</t>
+          <t>Tugalwala</t>
         </is>
       </c>
       <c r="C188" s="28" t="inlineStr">
         <is>
-          <t>ਤੁਗਲਵਾਲ</t>
+          <t>ਤੁਗਲਵਾਲਾ</t>
         </is>
       </c>
       <c r="D188" s="29" t="inlineStr">
@@ -11617,12 +11617,12 @@
       </c>
       <c r="B190" s="28" t="inlineStr">
         <is>
-          <t>Seeh Bhatti</t>
+          <t>Shih Bhatti</t>
         </is>
       </c>
       <c r="C190" s="28" t="inlineStr">
         <is>
-          <t>ਸੀਂਹ ਭੱਟੀ</t>
+          <t>ਸ਼ੀਂਹ ਭੱਟੀ</t>
         </is>
       </c>
       <c r="D190" s="39" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="B191" s="34" t="inlineStr">
         <is>
-          <t>Seeh Bhatti</t>
+          <t>Shihn Bhatti</t>
         </is>
       </c>
       <c r="C191" s="34" t="inlineStr">
         <is>
-          <t>ਸੀਂਹ ਭੱਟੀ</t>
+          <t>ਸ਼ੀਂਹ ਭੱਟੀ</t>
         </is>
       </c>
       <c r="D191" s="41" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="B194" s="28" t="inlineStr">
         <is>
-          <t>Thakkarwal</t>
+          <t>Thakarwal</t>
         </is>
       </c>
       <c r="C194" s="28" t="inlineStr">
         <is>
-          <t>ਠੱਕਰਵਾਲ</t>
+          <t>ਠਾਕਰਵਾਲ</t>
         </is>
       </c>
       <c r="D194" s="40" t="inlineStr">
@@ -11887,12 +11887,12 @@
       </c>
       <c r="B195" s="34" t="inlineStr">
         <is>
-          <t>Sooch</t>
+          <t>Sunch</t>
         </is>
       </c>
       <c r="C195" s="34" t="inlineStr">
         <is>
-          <t>ਸੂਚ</t>
+          <t>ਸੁੰਚ</t>
         </is>
       </c>
       <c r="D195" s="39" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="B196" s="28" t="inlineStr">
         <is>
-          <t>Datarpur, Bhochna</t>
+          <t>Datarpur</t>
         </is>
       </c>
       <c r="C196" s="28" t="inlineStr">
         <is>
-          <t>ਦਤਾਰਪੁਰ, ਭੋਚਨਾ</t>
+          <t>ਦਤਾਰਪੁਰ</t>
         </is>
       </c>
       <c r="D196" s="29" t="inlineStr">
@@ -12049,12 +12049,12 @@
       </c>
       <c r="B198" s="28" t="inlineStr">
         <is>
-          <t>Ferochechi</t>
+          <t>Phero Chechi</t>
         </is>
       </c>
       <c r="C198" s="28" t="inlineStr">
         <is>
-          <t>ਫੇਰੋਚੇਚੀ</t>
+          <t>ਫੇਰੋ ਚੇਚੀ</t>
         </is>
       </c>
       <c r="D198" s="39" t="inlineStr">
@@ -12103,12 +12103,12 @@
       </c>
       <c r="B199" s="34" t="inlineStr">
         <is>
-          <t>Jeendarh</t>
+          <t>Jindarh</t>
         </is>
       </c>
       <c r="C199" s="34" t="inlineStr">
         <is>
-          <t>ਜੀਂਦੜ</t>
+          <t>ਜਿੰਦੜ</t>
         </is>
       </c>
       <c r="D199" s="39" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="B200" s="28" t="inlineStr">
         <is>
-          <t>Ghorewah</t>
+          <t>Ghorhewah</t>
         </is>
       </c>
       <c r="C200" s="28" t="inlineStr">
@@ -12319,12 +12319,12 @@
       </c>
       <c r="B203" s="34" t="inlineStr">
         <is>
-          <t>Mehrey</t>
+          <t>Mehrhe</t>
         </is>
       </c>
       <c r="C203" s="34" t="inlineStr">
         <is>
-          <t>ਮੈਹੜੇ</t>
+          <t>ਮਹਿੜੇ</t>
         </is>
       </c>
       <c r="D203" s="41" t="inlineStr">
@@ -12589,12 +12589,12 @@
       </c>
       <c r="B208" s="28" t="inlineStr">
         <is>
-          <t>Dhandoi</t>
+          <t>Balwanda</t>
         </is>
       </c>
       <c r="C208" s="28" t="inlineStr">
         <is>
-          <t>ਧਾਂਦੋਈ</t>
+          <t>ਬਲਵੰਡਾ</t>
         </is>
       </c>
       <c r="D208" s="39" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="B209" s="34" t="inlineStr">
         <is>
-          <t>Chhichhda</t>
+          <t>Chhichra</t>
         </is>
       </c>
       <c r="C209" s="34" t="inlineStr">
         <is>
-          <t>ਛਿੱਛੜਾ</t>
+          <t>ਛਿੱਛਰਾ</t>
         </is>
       </c>
       <c r="D209" s="39" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="B210" s="28" t="inlineStr">
         <is>
-          <t>Raju Bela</t>
+          <t>Rajubela</t>
         </is>
       </c>
       <c r="C210" s="28" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="B211" s="34" t="inlineStr">
         <is>
-          <t>Alma</t>
+          <t>Aalma</t>
         </is>
       </c>
       <c r="C211" s="34" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="B212" s="28" t="inlineStr">
         <is>
-          <t>Awan, Salarpur, Bishanpur, Kisana, Dhore Kalian, Kotli Gujran</t>
+          <t>Awan</t>
         </is>
       </c>
       <c r="C212" s="28" t="inlineStr">
         <is>
-          <t>ਅਵਾਣ, ਸਲਾਰਪੁਰ, ਬਿਸਨਪੁਰ, ਕਿਸਾਨਾ, ਧੋਰੇ ਕਲੀਆਂ, ਕੋਟਲੀ ਗੁਜਰਾਂ</t>
+          <t>ਅਵਾਣ</t>
         </is>
       </c>
       <c r="D212" s="39" t="inlineStr">
@@ -12913,12 +12913,12 @@
       </c>
       <c r="B214" s="28" t="inlineStr">
         <is>
-          <t>Navian Bagrian, Mitha</t>
+          <t>Nawian Bagrhian</t>
         </is>
       </c>
       <c r="C214" s="28" t="inlineStr">
         <is>
-          <t>ਨਵੀਆਂ ਬਗੜੀਆਂ, ਮਿਠਾ</t>
+          <t>ਨਵੀਆਂ ਬਾਗੜੀਆਂ</t>
         </is>
       </c>
       <c r="D214" s="39" t="inlineStr">
@@ -12967,12 +12967,12 @@
       </c>
       <c r="B215" s="34" t="inlineStr">
         <is>
-          <t>Bagrian</t>
+          <t>Bagrhia</t>
         </is>
       </c>
       <c r="C215" s="34" t="inlineStr">
         <is>
-          <t>ਬਾਗੜੀਆਂ</t>
+          <t>ਬਾਗੜੀਆ</t>
         </is>
       </c>
       <c r="D215" s="39" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="B216" s="28" t="inlineStr">
         <is>
-          <t>Bagrian</t>
+          <t>Bagrhia</t>
         </is>
       </c>
       <c r="C216" s="28" t="inlineStr">
         <is>
-          <t>ਬਾਗੜੀਆਂ</t>
+          <t>ਬਾਗੜੀਆ</t>
         </is>
       </c>
       <c r="D216" s="39" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="B219" s="34" t="inlineStr">
         <is>
-          <t>Mullanwal</t>
+          <t>Mulanwal</t>
         </is>
       </c>
       <c r="C219" s="34" t="inlineStr">
         <is>
-          <t>ਮੁੱਲਾਂਵਾਲ</t>
+          <t>ਮੁਲਾਂਵਾਲ</t>
         </is>
       </c>
       <c r="D219" s="40" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B223" s="34" t="inlineStr">
         <is>
-          <t>Munnan, Ghulla Thatha</t>
+          <t>Munnan</t>
         </is>
       </c>
       <c r="C223" s="34" t="inlineStr">
         <is>
-          <t>ਮੁੰਨਣ, ਘੁੱਲਾ ਥਾਥਾ</t>
+          <t>ਮੁੰਨਣ</t>
         </is>
       </c>
       <c r="D223" s="40" t="inlineStr">
@@ -13581,8 +13581,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>Allowal</t>
+          <t>Alowal</t>
         </is>
       </c>
       <c r="C4" s="28" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>Allowal</t>
+          <t>Alowal</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>Kheh Tikha + Chakk Gharoye</t>
+          <t>Theh Tikha</t>
         </is>
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>ਖੇਹ ਤਿੱਖਾ + ਚੱਕ ਘਰੋਏ</t>
+          <t>ਥੇਹ ਤਿੱਖਾ</t>
         </is>
       </c>
       <c r="D8" s="29" t="inlineStr">
@@ -14052,12 +14052,12 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Chakk Deepewal + Devidaspur</t>
+          <t>Chak Dipewal</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਦੀਪੇਵਾਲ + ਦੇਵੀਦਾਸਪੁਰ</t>
+          <t>ਚੱਕ ਦੀਪੇਵਾਲ</t>
         </is>
       </c>
       <c r="D9" s="41" t="inlineStr">
@@ -14484,12 +14484,12 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Kalyanpur</t>
+          <t>Kalayanpur</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>ਕਲਿਆਨਪੁਰ</t>
+          <t>ਕਲਿਆਣਪੁਰ</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>ਕਲਿਆਨਪੁਰ</t>
+          <t>ਕਲਿਆਣਪੁਰ</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
@@ -14592,12 +14592,12 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D19" s="41" t="inlineStr">
@@ -14646,12 +14646,12 @@
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D20" s="29" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D21" s="29" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>Mahandev Kalan</t>
+          <t>Mahadev Kalan</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="B30" s="28" t="inlineStr">
         <is>
-          <t>Trija Nagar + Rania</t>
+          <t>Trija Nagar</t>
         </is>
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>ਤਰੀਜਾ ਨੰਗਰ + ਰਣੀਆ</t>
+          <t>ਤਰੀਜਾ ਨਗਰ</t>
         </is>
       </c>
       <c r="D30" s="41" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
@@ -15294,12 +15294,12 @@
       </c>
       <c r="B32" s="28" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>ਰਣੀਆ</t>
+          <t>ਰਣੀਆਂ</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Daddwan</t>
+          <t>Dadwan</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>Daddwan</t>
+          <t>Dadwan</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
@@ -16428,7 +16428,7 @@
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Ahmadabad</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="B59" s="34" t="inlineStr">
         <is>
-          <t>Sujanpur, Maali Samrai</t>
+          <t>Sujanpur</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>ਸੁਜਾਨਪੁਰ, ਮਾਲੀ ਸਮਰਾਏ</t>
+          <t>ਸੁਜਾਨਪੁਰ</t>
         </is>
       </c>
       <c r="D59" s="38" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Badoye</t>
+          <t>Baroya</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
@@ -17454,12 +17454,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Faizulla Chak</t>
+          <t>Faij Ulla Chak</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>ਫੈਜੁੱਲਾ ਚੱਕ</t>
+          <t>ਫੈਜ਼ੁੱਲਾ ਚੱਕ</t>
         </is>
       </c>
       <c r="D72" s="41" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>Faizulla Chak</t>
+          <t>Faij Ulla Chak</t>
         </is>
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>ਫੈਜੁੱਲਾ ਚੱਕ</t>
+          <t>ਫੈਜ਼ੁੱਲਾ ਚੱਕ</t>
         </is>
       </c>
       <c r="D73" s="38" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>ਡੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
+          <t>ਦੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
         </is>
       </c>
       <c r="D74" s="39" t="inlineStr">
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C75" s="34" t="inlineStr">
         <is>
-          <t>ਡੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
+          <t>ਦੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
         </is>
       </c>
       <c r="D75" s="39" t="inlineStr">
@@ -17670,12 +17670,12 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>Khan Mallak</t>
+          <t>Khan Malak</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>ਖਾਨ ਮੱਲਕ</t>
+          <t>ਖਾਨ ਮਲਕ</t>
         </is>
       </c>
       <c r="D76" s="41" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="B77" s="34" t="inlineStr">
         <is>
-          <t>Pasnawal</t>
+          <t>Pasnawala</t>
         </is>
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
-          <t>ਪਸਨਾਵਾਲ</t>
+          <t>ਪਸਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D77" s="41" t="inlineStr">
@@ -17778,12 +17778,12 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>Pasnawal</t>
+          <t>Pasnawala</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>ਪਸਨਾਵਾਲ</t>
+          <t>ਪਸਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D78" s="39" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="C81" s="34" t="inlineStr">
         <is>
-          <t>ਗਿਲ ਮੰਝ</t>
+          <t>ਗਿੱਲ ਮੰਜ</t>
         </is>
       </c>
       <c r="D81" s="29" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>ਛੀਨਾ ਰੇਤ ਵਾਲਾ</t>
+          <t>ਛੀਨਾ ਰੇਤਵਾਲਾ</t>
         </is>
       </c>
       <c r="D82" s="38" t="inlineStr">
@@ -18048,12 +18048,12 @@
       </c>
       <c r="B83" s="34" t="inlineStr">
         <is>
-          <t>Thakkar Sandhu</t>
+          <t>Thakar Sandhu</t>
         </is>
       </c>
       <c r="C83" s="34" t="inlineStr">
         <is>
-          <t>ਠੱਕਰ ਸੰਧੂ</t>
+          <t>ਠਾਕਰ ਸੰਧੂ</t>
         </is>
       </c>
       <c r="D83" s="41" t="inlineStr">
@@ -18210,12 +18210,12 @@
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>Jogi Cheema + Chamiyari</t>
+          <t>Jogi Cheema</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>ਜੋਗੀ ਚੀਮਾ + ਚਮਿਆਰੀ</t>
+          <t>ਜੋਗੀ ਚੀਮਾ</t>
         </is>
       </c>
       <c r="D86" s="38" t="inlineStr">
@@ -18318,12 +18318,12 @@
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>Balaggan</t>
+          <t>Balagan</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
         <is>
-          <t>ਬਲੱਗਣ</t>
+          <t>ਬਲਾਗਣ</t>
         </is>
       </c>
       <c r="D88" s="41" t="inlineStr">
@@ -18480,7 +18480,7 @@
       </c>
       <c r="B91" s="34" t="inlineStr">
         <is>
-          <t>Duluana</t>
+          <t>Duluaana</t>
         </is>
       </c>
       <c r="C91" s="34" t="inlineStr">
@@ -18534,12 +18534,12 @@
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>Sahaipur, Langarkot, Haveli Harni</t>
+          <t>Sahaipur</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>ਸਹਾਈਪੁਰ, ਲੰਗਰਕੋਟ, ਹਵੇਲੀ ਹਾਰਨੀ</t>
+          <t>ਸਹਾਈਪੁਰ</t>
         </is>
       </c>
       <c r="D92" s="39" t="inlineStr">
@@ -18588,12 +18588,12 @@
       </c>
       <c r="B93" s="34" t="inlineStr">
         <is>
-          <t>Bhikari Harni, Saidpur Harni, Bhore Harni</t>
+          <t>Bhikhari Harni</t>
         </is>
       </c>
       <c r="C93" s="34" t="inlineStr">
         <is>
-          <t>ਭਿਖਾਰੀ ਹਾਰਨੀ, ਸੈਦਪੁਰ ਹਾਰਨੀ, ਭੋਰੇ ਹਾਰਨੀ</t>
+          <t>ਭਿਖਾਰੀ ਹਾਰਨੀ</t>
         </is>
       </c>
       <c r="D93" s="41" t="inlineStr">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>Chhorian Bangar</t>
+          <t>Chhaurian Bangar</t>
         </is>
       </c>
       <c r="C104" s="28" t="inlineStr">
         <is>
-          <t>ਛੋੜੀਆ ਬਾਂਗਰ</t>
+          <t>ਛੌੜੀਆਂ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D104" s="38" t="inlineStr">
@@ -19236,12 +19236,12 @@
       </c>
       <c r="B105" s="34" t="inlineStr">
         <is>
-          <t>Kotli Siania</t>
+          <t>Kotli Sainian</t>
         </is>
       </c>
       <c r="C105" s="34" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸਿਆਣੀਆਂ</t>
+          <t>ਕੋਟਲੀ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D105" s="39" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>Kotli Siania</t>
+          <t>Kotli Sainian</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸਿਆਣੀਆਂ</t>
+          <t>ਕੋਟਲੀ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D106" s="40" t="inlineStr">
@@ -19398,12 +19398,12 @@
       </c>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>Saidowal Khurd, Bhaini Kaniya, Chakk Abdul</t>
+          <t>Bhaini Kanian</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
         <is>
-          <t>ਸੈਦੋਵਾਲ ਖੁਰਦ, ਭੈਣੀ ਕਾਨੀਆਂ, ਚੱਕ ਅਬਦੁਲ</t>
+          <t>ਭੈਣੀ ਕਾਨੀਆਂ</t>
         </is>
       </c>
       <c r="D108" s="39" t="inlineStr">
@@ -19452,12 +19452,12 @@
       </c>
       <c r="B109" s="34" t="inlineStr">
         <is>
-          <t>Darapur, Jangal</t>
+          <t>Darapur</t>
         </is>
       </c>
       <c r="C109" s="34" t="inlineStr">
         <is>
-          <t>ਦਾਰਾਪੁਰ, ਜੰਗਲ</t>
+          <t>ਦਾਰਾਪੁਰ</t>
         </is>
       </c>
       <c r="D109" s="38" t="inlineStr">
@@ -19506,12 +19506,12 @@
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>Gulepur, Gargarian</t>
+          <t>Gunopur</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
         <is>
-          <t>ਗੁਲੇਪੁਰ, ਗਾਰਗੜੀਆਂ</t>
+          <t>ਗੁਨੋਪੁਰ</t>
         </is>
       </c>
       <c r="D110" s="29" t="inlineStr">
@@ -19560,12 +19560,12 @@
       </c>
       <c r="B111" s="34" t="inlineStr">
         <is>
-          <t>Gulepur</t>
+          <t>Gunopur</t>
         </is>
       </c>
       <c r="C111" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਲੇਪੁਰ</t>
+          <t>ਗੁਨੋਪੁਰ</t>
         </is>
       </c>
       <c r="D111" s="41" t="inlineStr">
@@ -19668,12 +19668,12 @@
       </c>
       <c r="B113" s="34" t="inlineStr">
         <is>
-          <t>Jagowal Bet, Jaati Sarai, Bhuriya Gujran</t>
+          <t>Jagowal Bet</t>
         </is>
       </c>
       <c r="C113" s="34" t="inlineStr">
         <is>
-          <t>ਜਾਗੋਵਾਲ ਬੇਟ, ਜਾਤੀ ਸਰਾਏ, ਭੂਰੀਆ ਗੁਜਰਾਂ</t>
+          <t>ਜਾਗੋਵਾਲ ਬੇਟ</t>
         </is>
       </c>
       <c r="D113" s="41" t="inlineStr">
@@ -19776,12 +19776,12 @@
       </c>
       <c r="B115" s="34" t="inlineStr">
         <is>
-          <t>Bhaini Paswal, Randhawa Colony</t>
+          <t>Bhaini Paswal</t>
         </is>
       </c>
       <c r="C115" s="34" t="inlineStr">
         <is>
-          <t>ਭੈਣੀ ਪਸਵਾਲ, ਰੰਧਾਵਾ ਕਲੋਨੀ</t>
+          <t>ਭੈਣੀ ਪਸਵਾਲ</t>
         </is>
       </c>
       <c r="D115" s="39" t="inlineStr">
@@ -19830,12 +19830,12 @@
       </c>
       <c r="B116" s="28" t="inlineStr">
         <is>
-          <t>Kishanpur, Kathana, Yodhe</t>
+          <t>Kishanpur</t>
         </is>
       </c>
       <c r="C116" s="28" t="inlineStr">
         <is>
-          <t>ਕਿਸ਼ਨਪੁਰ, ਕਠਾਣਾ, ਯੋਧੇ</t>
+          <t>ਕਿਸ਼ਨਪੁਰ</t>
         </is>
       </c>
       <c r="D116" s="38" t="inlineStr">
@@ -19884,12 +19884,12 @@
       </c>
       <c r="B117" s="34" t="inlineStr">
         <is>
-          <t>Munan Kalan</t>
+          <t>Munnan Kalan</t>
         </is>
       </c>
       <c r="C117" s="34" t="inlineStr">
         <is>
-          <t>ਮੰਨਣ ਕਲਾਂ</t>
+          <t>ਮੁੰਨਣ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D117" s="38" t="inlineStr">
@@ -19938,12 +19938,12 @@
       </c>
       <c r="B118" s="28" t="inlineStr">
         <is>
-          <t>Bujarh</t>
+          <t>Bajar</t>
         </is>
       </c>
       <c r="C118" s="28" t="inlineStr">
         <is>
-          <t>ਬੁਜਾੜ</t>
+          <t>ਬਾਜੜ</t>
         </is>
       </c>
       <c r="D118" s="38" t="inlineStr">
@@ -19992,12 +19992,12 @@
       </c>
       <c r="B119" s="34" t="inlineStr">
         <is>
-          <t>Baruhia Molian, Piro Nangal, Sarwarpur, Bhulripur, Bhum</t>
+          <t>Bhurian Sainia</t>
         </is>
       </c>
       <c r="C119" s="34" t="inlineStr">
         <is>
-          <t>ਬਰੂਹੀਆ ਮੋਲੀਆਂ, ਪੀਰੋ ਨੰਗਲ, ਸਰਵਰਪੁਰ, ਭੁਲੜੀਪੁਰ, ਭੂਮ</t>
+          <t>ਭੂਰੀਆਂ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D119" s="41" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="C120" s="28" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਸਰੀਫ</t>
+          <t>ਚੱਕ ਸ਼ਰੀਫ</t>
         </is>
       </c>
       <c r="D120" s="39" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="C121" s="34" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਸਰੀਫ</t>
+          <t>ਚੱਕ ਸ਼ਰੀਫ</t>
         </is>
       </c>
       <c r="D121" s="38" t="inlineStr">
@@ -20154,12 +20154,12 @@
       </c>
       <c r="B122" s="28" t="inlineStr">
         <is>
-          <t>Kotla Gujran, Jhanda Gujran</t>
+          <t>Kotla Gujran</t>
         </is>
       </c>
       <c r="C122" s="28" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਗੁਜਰਾਂ, ਝੰਡਾ ਗੁਜਰਾਂ</t>
+          <t>ਕੋਟਲਾ ਗੁਜਰਾਂ</t>
         </is>
       </c>
       <c r="D122" s="38" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="B125" s="34" t="inlineStr">
         <is>
-          <t>Kotli Garhwan</t>
+          <t>Kotli Ralwan</t>
         </is>
       </c>
       <c r="C125" s="34" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਗਰਲਵਾਂ</t>
+          <t>ਕੋਟਲੀ ਰਲਵਾਂ</t>
         </is>
       </c>
       <c r="D125" s="38" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="B126" s="28" t="inlineStr">
         <is>
-          <t>Chak Yakub</t>
+          <t>Chak Yaqub</t>
         </is>
       </c>
       <c r="C126" s="28" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="C127" s="34" t="inlineStr">
         <is>
-          <t>ਲਾਧੂਪੁਰ</t>
+          <t>ਲੱਧੂਪੁਰ</t>
         </is>
       </c>
       <c r="D127" s="39" t="inlineStr">
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C128" s="28" t="inlineStr">
         <is>
-          <t>ਨੈਨੇਕੋਟ</t>
+          <t>ਨੈਣੇਕੋਟ</t>
         </is>
       </c>
       <c r="D128" s="41" t="inlineStr">
@@ -20586,12 +20586,12 @@
       </c>
       <c r="B130" s="28" t="inlineStr">
         <is>
-          <t>Raowal</t>
+          <t>Rauwal</t>
         </is>
       </c>
       <c r="C130" s="28" t="inlineStr">
         <is>
-          <t>ਰਾਓਵਾਲ</t>
+          <t>ਰਾਊਵਾਲ</t>
         </is>
       </c>
       <c r="D130" s="38" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C131" s="34" t="inlineStr">
         <is>
-          <t>ਨਿਮਾਣੇ</t>
+          <t>ਨੀਮਾਣੇ</t>
         </is>
       </c>
       <c r="D131" s="39" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="B133" s="34" t="inlineStr">
         <is>
-          <t>Bhittewadd</t>
+          <t>Bhite Wad</t>
         </is>
       </c>
       <c r="C133" s="34" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="B134" s="28" t="inlineStr">
         <is>
-          <t>Kot Todar Mal</t>
+          <t>Kot Todar Mall</t>
         </is>
       </c>
       <c r="C134" s="28" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="B135" s="34" t="inlineStr">
         <is>
-          <t>Kot Todar Mal</t>
+          <t>Kot Todar Mall</t>
         </is>
       </c>
       <c r="C135" s="34" t="inlineStr">
@@ -20910,12 +20910,12 @@
       </c>
       <c r="B136" s="28" t="inlineStr">
         <is>
-          <t>Rooda Buttar</t>
+          <t>Rurha Buttar</t>
         </is>
       </c>
       <c r="C136" s="28" t="inlineStr">
         <is>
-          <t>ਰੂੜਾ ਬੁੱਟਰ</t>
+          <t>ਰੂੜ੍ਹਾ ਬੁੱਟਰ</t>
         </is>
       </c>
       <c r="D136" s="38" t="inlineStr">
@@ -20964,12 +20964,12 @@
       </c>
       <c r="B137" s="34" t="inlineStr">
         <is>
-          <t>Malian</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="C137" s="34" t="inlineStr">
         <is>
-          <t>ਮਾਲੀਆਂ</t>
+          <t>ਮਾਲੀਆ</t>
         </is>
       </c>
       <c r="D137" s="41" t="inlineStr">
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B140" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 4</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C140" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 4</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D140" s="29" t="inlineStr">
@@ -21180,12 +21180,12 @@
       </c>
       <c r="B141" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 2</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C141" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 2</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D141" s="41" t="inlineStr">
@@ -21234,12 +21234,12 @@
       </c>
       <c r="B142" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 2</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C142" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 2</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D142" s="41" t="inlineStr">
@@ -21288,12 +21288,12 @@
       </c>
       <c r="B143" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 1</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C143" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 1</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D143" s="39" t="inlineStr">
@@ -21342,12 +21342,12 @@
       </c>
       <c r="B144" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 7</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C144" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 7</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D144" s="40" t="inlineStr">
@@ -21396,12 +21396,12 @@
       </c>
       <c r="B145" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 8</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C145" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 8</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D145" s="38" t="inlineStr">
@@ -21450,12 +21450,12 @@
       </c>
       <c r="B146" s="28" t="inlineStr">
         <is>
-          <t>Qadian Civil Lines</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C146" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਸਿਵਲ ਲਾਈਨ</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D146" s="40" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="B147" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 6</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C147" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 6</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D147" s="40" t="inlineStr">
@@ -21558,12 +21558,12 @@
       </c>
       <c r="B148" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 5</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C148" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 5</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D148" s="41" t="inlineStr">
@@ -21612,12 +21612,12 @@
       </c>
       <c r="B149" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 5</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C149" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 5</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D149" s="41" t="inlineStr">
@@ -21666,12 +21666,12 @@
       </c>
       <c r="B150" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 11</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C150" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 11</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D150" s="41" t="inlineStr">
@@ -21720,12 +21720,12 @@
       </c>
       <c r="B151" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 10</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C151" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 10</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D151" s="38" t="inlineStr">
@@ -21774,12 +21774,12 @@
       </c>
       <c r="B152" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 12</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C152" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 12</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D152" s="38" t="inlineStr">
@@ -21828,12 +21828,12 @@
       </c>
       <c r="B153" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 9</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C153" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 9</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D153" s="38" t="inlineStr">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="B154" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 13</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C154" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 13</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D154" s="38" t="inlineStr">
@@ -21936,12 +21936,12 @@
       </c>
       <c r="B155" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 15</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C155" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 15</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D155" s="41" t="inlineStr">
@@ -21990,12 +21990,12 @@
       </c>
       <c r="B156" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 14</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C156" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 14</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D156" s="38" t="inlineStr">
@@ -22044,12 +22044,12 @@
       </c>
       <c r="B157" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 3</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C157" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 3</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D157" s="39" t="inlineStr">
@@ -22152,12 +22152,12 @@
       </c>
       <c r="B159" s="34" t="inlineStr">
         <is>
-          <t>Bhagatpura Rathwala</t>
+          <t>Patti Bhagtupur</t>
         </is>
       </c>
       <c r="C159" s="34" t="inlineStr">
         <is>
-          <t>ਭਗਤਪੁਰਾ ਰੱਥਵਾਲਾ</t>
+          <t>ਪੱਤੀ ਭਗਤੂਪੁਰ</t>
         </is>
       </c>
       <c r="D159" s="29" t="inlineStr">
@@ -22206,12 +22206,12 @@
       </c>
       <c r="B160" s="28" t="inlineStr">
         <is>
-          <t>Nangal Baghbana</t>
+          <t>Nangal Bagbana</t>
         </is>
       </c>
       <c r="C160" s="28" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਬਾਗਬਾਨਾ</t>
+          <t>ਨੰਗਲ ਬਾਗ਼ਬਾਨਾਂ</t>
         </is>
       </c>
       <c r="D160" s="38" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="B161" s="34" t="inlineStr">
         <is>
-          <t>Chhota Nangal</t>
+          <t>Chota Nangal</t>
         </is>
       </c>
       <c r="C161" s="34" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="B162" s="28" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C162" s="28" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="B163" s="34" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C163" s="34" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="B164" s="28" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C164" s="28" t="inlineStr">
@@ -22481,7 +22481,7 @@
       </c>
       <c r="C165" s="34" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D165" s="41" t="inlineStr">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="C166" s="28" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D166" s="29" t="inlineStr">
@@ -22589,7 +22589,7 @@
       </c>
       <c r="C167" s="34" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D167" s="41" t="inlineStr">
@@ -22638,12 +22638,12 @@
       </c>
       <c r="B168" s="28" t="inlineStr">
         <is>
-          <t>Daili Bangar</t>
+          <t>Bhaini Bangar</t>
         </is>
       </c>
       <c r="C168" s="28" t="inlineStr">
         <is>
-          <t>ਡੈਲੀ ਬਾਂਗਰ</t>
+          <t>ਭੈਣੀ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D168" s="40" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="B169" s="34" t="inlineStr">
         <is>
-          <t>Daili Bangar</t>
+          <t>Bhaini Banger</t>
         </is>
       </c>
       <c r="C169" s="34" t="inlineStr">
         <is>
-          <t>ਡੈਲੀ ਬਾਂਗਰ</t>
+          <t>ਭੈਣੀ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D169" s="39" t="inlineStr">
@@ -22800,12 +22800,12 @@
       </c>
       <c r="B171" s="34" t="inlineStr">
         <is>
-          <t>Salarpur</t>
+          <t>Salahpur</t>
         </is>
       </c>
       <c r="C171" s="34" t="inlineStr">
         <is>
-          <t>ਸਲਾਰਪੁਰ</t>
+          <t>ਸਲਾਹਪੁਰ</t>
         </is>
       </c>
       <c r="D171" s="41" t="inlineStr">
@@ -22854,12 +22854,12 @@
       </c>
       <c r="B172" s="28" t="inlineStr">
         <is>
-          <t>Chandogi Mayian Singh</t>
+          <t>Pandori Maiya Singh</t>
         </is>
       </c>
       <c r="C172" s="28" t="inlineStr">
         <is>
-          <t>ਚੰਡੋਗੀ ਮਈਆਂ ਸਿੰਘ</t>
+          <t>ਪੰਡੋਰੀ ਮਈਆਂ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D172" s="39" t="inlineStr">
@@ -22913,7 +22913,7 @@
       </c>
       <c r="C173" s="34" t="inlineStr">
         <is>
-          <t>ਕੂੰਟ</t>
+          <t>ਕੁੰਟ</t>
         </is>
       </c>
       <c r="D173" s="29" t="inlineStr">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="C174" s="28" t="inlineStr">
         <is>
-          <t>ਗੋਹਤ ਖੁਰਦ</t>
+          <t>ਘੋਟ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D174" s="41" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="B176" s="28" t="inlineStr">
         <is>
-          <t>Chib</t>
+          <t>Chibb</t>
         </is>
       </c>
       <c r="C176" s="28" t="inlineStr">
@@ -23129,7 +23129,7 @@
       </c>
       <c r="C177" s="34" t="inlineStr">
         <is>
-          <t>ਭੱਟੀਆਂ</t>
+          <t>ਭੱਠੀਆਂ</t>
         </is>
       </c>
       <c r="D177" s="29" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="C178" s="28" t="inlineStr">
         <is>
-          <t>ਭੱਟੀਆਂ</t>
+          <t>ਭੱਠੀਆਂ</t>
         </is>
       </c>
       <c r="D178" s="38" t="inlineStr">
@@ -23232,12 +23232,12 @@
       </c>
       <c r="B179" s="34" t="inlineStr">
         <is>
-          <t>Jangowal Bangar</t>
+          <t>Jagowal Bangar</t>
         </is>
       </c>
       <c r="C179" s="34" t="inlineStr">
         <is>
-          <t>ਜਾਂਗੋਵਾਲ ਬਾਂਗਰ</t>
+          <t>ਜਾਗੋਵਾਲ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D179" s="41" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="B180" s="28" t="inlineStr">
         <is>
-          <t>Kiri Afghana</t>
+          <t>Kiri Afgana</t>
         </is>
       </c>
       <c r="C180" s="28" t="inlineStr">
@@ -23448,12 +23448,12 @@
       </c>
       <c r="B183" s="34" t="inlineStr">
         <is>
-          <t>Ghukkan</t>
+          <t>Ghookla</t>
         </is>
       </c>
       <c r="C183" s="34" t="inlineStr">
         <is>
-          <t>ਘੁੱਕਲਾਂ</t>
+          <t>ਘੂਕਲਾ</t>
         </is>
       </c>
       <c r="D183" s="38" t="inlineStr">
@@ -23664,12 +23664,12 @@
       </c>
       <c r="B187" s="34" t="inlineStr">
         <is>
-          <t>Tugalwal</t>
+          <t>Tugalwala</t>
         </is>
       </c>
       <c r="C187" s="34" t="inlineStr">
         <is>
-          <t>ਤੁਗਲਵਾਲ</t>
+          <t>ਤੁਗਲਵਾਲਾ</t>
         </is>
       </c>
       <c r="D187" s="29" t="inlineStr">
@@ -23718,12 +23718,12 @@
       </c>
       <c r="B188" s="28" t="inlineStr">
         <is>
-          <t>Tugalwal</t>
+          <t>Tugalwala</t>
         </is>
       </c>
       <c r="C188" s="28" t="inlineStr">
         <is>
-          <t>ਤੁਗਲਵਾਲ</t>
+          <t>ਤੁਗਲਵਾਲਾ</t>
         </is>
       </c>
       <c r="D188" s="39" t="inlineStr">
@@ -23826,12 +23826,12 @@
       </c>
       <c r="B190" s="28" t="inlineStr">
         <is>
-          <t>Seeh Bhatti</t>
+          <t>Shih Bhatti</t>
         </is>
       </c>
       <c r="C190" s="28" t="inlineStr">
         <is>
-          <t>ਸੀਂਹ ਭੱਟੀ</t>
+          <t>ਸ਼ੀਂਹ ਭੱਟੀ</t>
         </is>
       </c>
       <c r="D190" s="41" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="B191" s="34" t="inlineStr">
         <is>
-          <t>Seeh Bhatti</t>
+          <t>Shihn Bhatti</t>
         </is>
       </c>
       <c r="C191" s="34" t="inlineStr">
         <is>
-          <t>ਸੀਂਹ ਭੱਟੀ</t>
+          <t>ਸ਼ੀਂਹ ਭੱਟੀ</t>
         </is>
       </c>
       <c r="D191" s="39" t="inlineStr">
@@ -24042,12 +24042,12 @@
       </c>
       <c r="B194" s="28" t="inlineStr">
         <is>
-          <t>Thakkarwal</t>
+          <t>Thakarwal</t>
         </is>
       </c>
       <c r="C194" s="28" t="inlineStr">
         <is>
-          <t>ਠੱਕਰਵਾਲ</t>
+          <t>ਠਾਕਰਵਾਲ</t>
         </is>
       </c>
       <c r="D194" s="29" t="inlineStr">
@@ -24096,12 +24096,12 @@
       </c>
       <c r="B195" s="34" t="inlineStr">
         <is>
-          <t>Sooch</t>
+          <t>Sunch</t>
         </is>
       </c>
       <c r="C195" s="34" t="inlineStr">
         <is>
-          <t>ਸੂਚ</t>
+          <t>ਸੁੰਚ</t>
         </is>
       </c>
       <c r="D195" s="29" t="inlineStr">
@@ -24150,12 +24150,12 @@
       </c>
       <c r="B196" s="28" t="inlineStr">
         <is>
-          <t>Datarpur, Bhochna</t>
+          <t>Datarpur</t>
         </is>
       </c>
       <c r="C196" s="28" t="inlineStr">
         <is>
-          <t>ਦਤਾਰਪੁਰ, ਭੋਚਨਾ</t>
+          <t>ਦਤਾਰਪੁਰ</t>
         </is>
       </c>
       <c r="D196" s="38" t="inlineStr">
@@ -24258,12 +24258,12 @@
       </c>
       <c r="B198" s="28" t="inlineStr">
         <is>
-          <t>Ferochechi</t>
+          <t>Phero Chechi</t>
         </is>
       </c>
       <c r="C198" s="28" t="inlineStr">
         <is>
-          <t>ਫੇਰੋਚੇਚੀ</t>
+          <t>ਫੇਰੋ ਚੇਚੀ</t>
         </is>
       </c>
       <c r="D198" s="41" t="inlineStr">
@@ -24312,12 +24312,12 @@
       </c>
       <c r="B199" s="34" t="inlineStr">
         <is>
-          <t>Jeendarh</t>
+          <t>Jindarh</t>
         </is>
       </c>
       <c r="C199" s="34" t="inlineStr">
         <is>
-          <t>ਜੀਂਦੜ</t>
+          <t>ਜਿੰਦੜ</t>
         </is>
       </c>
       <c r="D199" s="41" t="inlineStr">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="B200" s="28" t="inlineStr">
         <is>
-          <t>Ghorewah</t>
+          <t>Ghorhewah</t>
         </is>
       </c>
       <c r="C200" s="28" t="inlineStr">
@@ -24528,12 +24528,12 @@
       </c>
       <c r="B203" s="34" t="inlineStr">
         <is>
-          <t>Mehrey</t>
+          <t>Mehrhe</t>
         </is>
       </c>
       <c r="C203" s="34" t="inlineStr">
         <is>
-          <t>ਮੈਹੜੇ</t>
+          <t>ਮਹਿੜੇ</t>
         </is>
       </c>
       <c r="D203" s="39" t="inlineStr">
@@ -24798,12 +24798,12 @@
       </c>
       <c r="B208" s="28" t="inlineStr">
         <is>
-          <t>Dhandoi</t>
+          <t>Balwanda</t>
         </is>
       </c>
       <c r="C208" s="28" t="inlineStr">
         <is>
-          <t>ਧਾਂਦੋਈ</t>
+          <t>ਬਲਵੰਡਾ</t>
         </is>
       </c>
       <c r="D208" s="41" t="inlineStr">
@@ -24852,12 +24852,12 @@
       </c>
       <c r="B209" s="34" t="inlineStr">
         <is>
-          <t>Chhichhda</t>
+          <t>Chhichra</t>
         </is>
       </c>
       <c r="C209" s="34" t="inlineStr">
         <is>
-          <t>ਛਿੱਛੜਾ</t>
+          <t>ਛਿੱਛਰਾ</t>
         </is>
       </c>
       <c r="D209" s="41" t="inlineStr">
@@ -24906,7 +24906,7 @@
       </c>
       <c r="B210" s="28" t="inlineStr">
         <is>
-          <t>Raju Bela</t>
+          <t>Rajubela</t>
         </is>
       </c>
       <c r="C210" s="28" t="inlineStr">
@@ -24960,7 +24960,7 @@
       </c>
       <c r="B211" s="34" t="inlineStr">
         <is>
-          <t>Alma</t>
+          <t>Aalma</t>
         </is>
       </c>
       <c r="C211" s="34" t="inlineStr">
@@ -25014,12 +25014,12 @@
       </c>
       <c r="B212" s="28" t="inlineStr">
         <is>
-          <t>Awan, Salarpur, Bishanpur, Kisana, Dhore Kalian, Kotli Gujran</t>
+          <t>Awan</t>
         </is>
       </c>
       <c r="C212" s="28" t="inlineStr">
         <is>
-          <t>ਅਵਾਣ, ਸਲਾਰਪੁਰ, ਬਿਸਨਪੁਰ, ਕਿਸਾਨਾ, ਧੋਰੇ ਕਲੀਆਂ, ਕੋਟਲੀ ਗੁਜਰਾਂ</t>
+          <t>ਅਵਾਣ</t>
         </is>
       </c>
       <c r="D212" s="41" t="inlineStr">
@@ -25122,12 +25122,12 @@
       </c>
       <c r="B214" s="28" t="inlineStr">
         <is>
-          <t>Navian Bagrian, Mitha</t>
+          <t>Nawian Bagrhian</t>
         </is>
       </c>
       <c r="C214" s="28" t="inlineStr">
         <is>
-          <t>ਨਵੀਆਂ ਬਗੜੀਆਂ, ਮਿਠਾ</t>
+          <t>ਨਵੀਆਂ ਬਾਗੜੀਆਂ</t>
         </is>
       </c>
       <c r="D214" s="41" t="inlineStr">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B215" s="34" t="inlineStr">
         <is>
-          <t>Bagrian</t>
+          <t>Bagrhia</t>
         </is>
       </c>
       <c r="C215" s="34" t="inlineStr">
         <is>
-          <t>ਬਾਗੜੀਆਂ</t>
+          <t>ਬਾਗੜੀਆ</t>
         </is>
       </c>
       <c r="D215" s="38" t="inlineStr">
@@ -25230,12 +25230,12 @@
       </c>
       <c r="B216" s="28" t="inlineStr">
         <is>
-          <t>Bagrian</t>
+          <t>Bagrhia</t>
         </is>
       </c>
       <c r="C216" s="28" t="inlineStr">
         <is>
-          <t>ਬਾਗੜੀਆਂ</t>
+          <t>ਬਾਗੜੀਆ</t>
         </is>
       </c>
       <c r="D216" s="41" t="inlineStr">
@@ -25392,12 +25392,12 @@
       </c>
       <c r="B219" s="34" t="inlineStr">
         <is>
-          <t>Mullanwal</t>
+          <t>Mulanwal</t>
         </is>
       </c>
       <c r="C219" s="34" t="inlineStr">
         <is>
-          <t>ਮੁੱਲਾਂਵਾਲ</t>
+          <t>ਮੁਲਾਂਵਾਲ</t>
         </is>
       </c>
       <c r="D219" s="29" t="inlineStr">
@@ -25608,12 +25608,12 @@
       </c>
       <c r="B223" s="34" t="inlineStr">
         <is>
-          <t>Munnan, Ghulla Thatha</t>
+          <t>Munnan</t>
         </is>
       </c>
       <c r="C223" s="34" t="inlineStr">
         <is>
-          <t>ਮੁੰਨਣ, ਘੁੱਲਾ ਥਾਥਾ</t>
+          <t>ਮੁੰਨਣ</t>
         </is>
       </c>
       <c r="D223" s="41" t="inlineStr">
@@ -25790,8 +25790,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -26126,12 +26126,12 @@
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D10" s="30" t="n">
@@ -26174,12 +26174,12 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D11" s="35" t="n">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="B16" s="28" t="inlineStr">
         <is>
-          <t>Mahandev Kalan</t>
+          <t>Mahadev Kalan</t>
         </is>
       </c>
       <c r="C16" s="28" t="inlineStr">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="B18" s="28" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="C18" s="28" t="inlineStr">
@@ -27134,7 +27134,7 @@
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Ahmadabad</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
@@ -27182,7 +27182,7 @@
       </c>
       <c r="B32" s="28" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C32" s="28" t="inlineStr">
@@ -27235,7 +27235,7 @@
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>ਡੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
+          <t>ਦੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
         </is>
       </c>
       <c r="D33" s="35" t="n">
@@ -27283,7 +27283,7 @@
       </c>
       <c r="C34" s="28" t="inlineStr">
         <is>
-          <t>ਡੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
+          <t>ਦੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
         </is>
       </c>
       <c r="D34" s="30" t="n">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>Duluana</t>
+          <t>Duluaana</t>
         </is>
       </c>
       <c r="C35" s="34" t="inlineStr">
@@ -27374,12 +27374,12 @@
       </c>
       <c r="B36" s="28" t="inlineStr">
         <is>
-          <t>Sahaipur, Langarkot, Haveli Harni</t>
+          <t>Sahaipur</t>
         </is>
       </c>
       <c r="C36" s="28" t="inlineStr">
         <is>
-          <t>ਸਹਾਈਪੁਰ, ਲੰਗਰਕੋਟ, ਹਵੇਲੀ ਹਾਰਨੀ</t>
+          <t>ਸਹਾਈਪੁਰ</t>
         </is>
       </c>
       <c r="D36" s="30" t="n">
@@ -27662,12 +27662,12 @@
       </c>
       <c r="B42" s="28" t="inlineStr">
         <is>
-          <t>Saidowal Khurd, Bhaini Kaniya, Chakk Abdul</t>
+          <t>Bhaini Kanian</t>
         </is>
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>ਸੈਦੋਵਾਲ ਖੁਰਦ, ਭੈਣੀ ਕਾਨੀਆਂ, ਚੱਕ ਅਬਦੁਲ</t>
+          <t>ਭੈਣੀ ਕਾਨੀਆਂ</t>
         </is>
       </c>
       <c r="D42" s="30" t="n">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਸਰੀਫ</t>
+          <t>ਚੱਕ ਸ਼ਰੀਫ</t>
         </is>
       </c>
       <c r="D44" s="30" t="n">
@@ -27806,12 +27806,12 @@
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>Kotla Gujran, Jhanda Gujran</t>
+          <t>Kotla Gujran</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਗੁਜਰਾਂ, ਝੰਡਾ ਗੁਜਰਾਂ</t>
+          <t>ਕੋਟਲਾ ਗੁਜਰਾਂ</t>
         </is>
       </c>
       <c r="D45" s="35" t="n">
@@ -27854,12 +27854,12 @@
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>Kotli Garhwan</t>
+          <t>Kotli Ralwan</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਗਰਲਵਾਂ</t>
+          <t>ਕੋਟਲੀ ਰਲਵਾਂ</t>
         </is>
       </c>
       <c r="D46" s="30" t="n">
@@ -27907,7 +27907,7 @@
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>ਨਿਮਾਣੇ</t>
+          <t>ਨੀਮਾਣੇ</t>
         </is>
       </c>
       <c r="D47" s="35" t="n">
@@ -27950,7 +27950,7 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>Kot Todar Mal</t>
+          <t>Kot Todar Mall</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
@@ -27998,12 +27998,12 @@
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 7</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 7</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D49" s="35" t="n">
@@ -28046,12 +28046,12 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>Qadian Civil Lines</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਸਿਵਲ ਲਾਈਨ</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D50" s="30" t="n">
@@ -28094,12 +28094,12 @@
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 6</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 6</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D51" s="35" t="n">
@@ -28142,12 +28142,12 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 12</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 12</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D52" s="30" t="n">
@@ -28190,12 +28190,12 @@
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 9</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 9</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D53" s="35" t="n">
@@ -28238,12 +28238,12 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 13</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 13</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D54" s="30" t="n">
@@ -28286,12 +28286,12 @@
       </c>
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 14</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 14</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D55" s="35" t="n">
@@ -28387,7 +28387,7 @@
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D57" s="35" t="n">
@@ -28430,12 +28430,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Chandogi Mayian Singh</t>
+          <t>Pandori Maiya Singh</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>ਚੰਡੋਗੀ ਮਈਆਂ ਸਿੰਘ</t>
+          <t>ਪੰਡੋਰੀ ਮਈਆਂ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D58" s="30" t="n">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>ਕੂੰਟ</t>
+          <t>ਕੁੰਟ</t>
         </is>
       </c>
       <c r="D59" s="35" t="n">
@@ -28526,7 +28526,7 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>Chib</t>
+          <t>Chibb</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
@@ -28579,7 +28579,7 @@
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
-          <t>ਭੱਟੀਆਂ</t>
+          <t>ਭੱਠੀਆਂ</t>
         </is>
       </c>
       <c r="D61" s="35" t="n">
@@ -28622,7 +28622,7 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Kiri Afghana</t>
+          <t>Kiri Afgana</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
@@ -28766,12 +28766,12 @@
       </c>
       <c r="B65" s="34" t="inlineStr">
         <is>
-          <t>Ghukkan</t>
+          <t>Ghookla</t>
         </is>
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>ਘੁੱਕਲਾਂ</t>
+          <t>ਘੂਕਲਾ</t>
         </is>
       </c>
       <c r="D65" s="35" t="n">
@@ -28862,12 +28862,12 @@
       </c>
       <c r="B67" s="34" t="inlineStr">
         <is>
-          <t>Tugalwal</t>
+          <t>Tugalwala</t>
         </is>
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
-          <t>ਤੁਗਲਵਾਲ</t>
+          <t>ਤੁਗਲਵਾਲਾ</t>
         </is>
       </c>
       <c r="D67" s="35" t="n">
@@ -28910,12 +28910,12 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Tugalwal</t>
+          <t>Tugalwala</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>ਤੁਗਲਵਾਲ</t>
+          <t>ਤੁਗਲਵਾਲਾ</t>
         </is>
       </c>
       <c r="D68" s="30" t="n">
@@ -29102,12 +29102,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Thakkarwal</t>
+          <t>Thakarwal</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>ਠੱਕਰਵਾਲ</t>
+          <t>ਠਾਕਰਵਾਲ</t>
         </is>
       </c>
       <c r="D72" s="30" t="n">
@@ -29150,12 +29150,12 @@
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>Sooch</t>
+          <t>Sunch</t>
         </is>
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>ਸੂਚ</t>
+          <t>ਸੁੰਚ</t>
         </is>
       </c>
       <c r="D73" s="35" t="n">
@@ -29198,12 +29198,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>Bagrian</t>
+          <t>Bagrhia</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>ਬਾਗੜੀਆਂ</t>
+          <t>ਬਾਗੜੀਆ</t>
         </is>
       </c>
       <c r="D74" s="30" t="n">
@@ -29246,12 +29246,12 @@
       </c>
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>Mullanwal</t>
+          <t>Mulanwal</t>
         </is>
       </c>
       <c r="C75" s="34" t="inlineStr">
         <is>
-          <t>ਮੁੱਲਾਂਵਾਲ</t>
+          <t>ਮੁਲਾਂਵਾਲ</t>
         </is>
       </c>
       <c r="D75" s="35" t="n">
@@ -29399,8 +29399,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>Allowal</t>
+          <t>Alowal</t>
         </is>
       </c>
       <c r="C4" s="28" t="inlineStr">
@@ -29789,7 +29789,7 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>Allowal</t>
+          <t>Alowal</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
@@ -30032,12 +30032,12 @@
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>Kheh Tikha + Chakk Gharoye</t>
+          <t>Theh Tikha</t>
         </is>
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>ਖੇਹ ਤਿੱਖਾ + ਚੱਕ ਘਰੋਏ</t>
+          <t>ਥੇਹ ਤਿੱਖਾ</t>
         </is>
       </c>
       <c r="D8" s="30" t="n">
@@ -30113,12 +30113,12 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Chakk Deepewal + Devidaspur</t>
+          <t>Chak Dipewal</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਦੀਪੇਵਾਲ + ਦੇਵੀਦਾਸਪੁਰ</t>
+          <t>ਚੱਕ ਦੀਪੇਵਾਲ</t>
         </is>
       </c>
       <c r="D9" s="35" t="n">
@@ -30761,12 +30761,12 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Kalyanpur</t>
+          <t>Kalayanpur</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>ਕਲਿਆਨਪੁਰ</t>
+          <t>ਕਲਿਆਣਪੁਰ</t>
         </is>
       </c>
       <c r="D17" s="35" t="n">
@@ -30847,7 +30847,7 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>ਕਲਿਆਨਪੁਰ</t>
+          <t>ਕਲਿਆਣਪੁਰ</t>
         </is>
       </c>
       <c r="D18" s="30" t="n">
@@ -30923,12 +30923,12 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D19" s="35" t="n">
@@ -31004,12 +31004,12 @@
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D20" s="30" t="n">
@@ -31085,12 +31085,12 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>Gurdas Nangal + Badiyawala</t>
+          <t>Gurdas Nangal</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਰਦਾਸ ਨੰਗਲ + ਬੜੀਆਵਾਲਾ</t>
+          <t>ਗੁਰਦਾਸ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D21" s="35" t="n">
@@ -31652,7 +31652,7 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>Mahandev Kalan</t>
+          <t>Mahadev Kalan</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
@@ -31814,12 +31814,12 @@
       </c>
       <c r="B30" s="28" t="inlineStr">
         <is>
-          <t>Trija Nagar + Rania</t>
+          <t>Trija Nagar</t>
         </is>
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>ਤਰੀਜਾ ਨੰਗਰ + ਰਣੀਆ</t>
+          <t>ਤਰੀਜਾ ਨਗਰ</t>
         </is>
       </c>
       <c r="D30" s="30" t="n">
@@ -31895,7 +31895,7 @@
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
@@ -31976,12 +31976,12 @@
       </c>
       <c r="B32" s="28" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>ਰਣੀਆ</t>
+          <t>ਰਣੀਆਂ</t>
         </is>
       </c>
       <c r="D32" s="30" t="n">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Daddwan</t>
+          <t>Dadwan</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
@@ -33434,7 +33434,7 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>Daddwan</t>
+          <t>Dadwan</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
@@ -33677,7 +33677,7 @@
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Ahmadabad</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
@@ -34001,7 +34001,7 @@
       </c>
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
@@ -34082,7 +34082,7 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Fajju Pura</t>
+          <t>Fajjupura</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
@@ -34163,12 +34163,12 @@
       </c>
       <c r="B59" s="34" t="inlineStr">
         <is>
-          <t>Sujanpur, Maali Samrai</t>
+          <t>Sujanpur</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>ਸੁਜਾਨਪੁਰ, ਮਾਲੀ ਸਮਰਾਏ</t>
+          <t>ਸੁਜਾਨਪੁਰ</t>
         </is>
       </c>
       <c r="D59" s="35" t="n">
@@ -34730,7 +34730,7 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Badoye</t>
+          <t>Baroya</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
@@ -35216,12 +35216,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Faizulla Chak</t>
+          <t>Faij Ulla Chak</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>ਫੈਜੁੱਲਾ ਚੱਕ</t>
+          <t>ਫੈਜ਼ੁੱਲਾ ਚੱਕ</t>
         </is>
       </c>
       <c r="D72" s="30" t="n">
@@ -35297,12 +35297,12 @@
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>Faizulla Chak</t>
+          <t>Faij Ulla Chak</t>
         </is>
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>ਫੈਜੁੱਲਾ ਚੱਕ</t>
+          <t>ਫੈਜ਼ੁੱਲਾ ਚੱਕ</t>
         </is>
       </c>
       <c r="D73" s="35" t="n">
@@ -35383,7 +35383,7 @@
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>ਡੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
+          <t>ਦੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
         </is>
       </c>
       <c r="D74" s="30" t="n">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="C75" s="34" t="inlineStr">
         <is>
-          <t>ਡੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
+          <t>ਦੇਹਰੀਵਾਲ ਦਰੋਗਾ</t>
         </is>
       </c>
       <c r="D75" s="35" t="n">
@@ -35540,12 +35540,12 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>Khan Mallak</t>
+          <t>Khan Malak</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>ਖਾਨ ਮੱਲਕ</t>
+          <t>ਖਾਨ ਮਲਕ</t>
         </is>
       </c>
       <c r="D76" s="30" t="n">
@@ -35621,12 +35621,12 @@
       </c>
       <c r="B77" s="34" t="inlineStr">
         <is>
-          <t>Pasnawal</t>
+          <t>Pasnawala</t>
         </is>
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
-          <t>ਪਸਨਾਵਾਲ</t>
+          <t>ਪਸਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D77" s="35" t="n">
@@ -35702,12 +35702,12 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>Pasnawal</t>
+          <t>Pasnawala</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>ਪਸਨਾਵਾਲ</t>
+          <t>ਪਸਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D78" s="30" t="n">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="C81" s="34" t="inlineStr">
         <is>
-          <t>ਗਿਲ ਮੰਝ</t>
+          <t>ਗਿੱਲ ਮੰਜ</t>
         </is>
       </c>
       <c r="D81" s="35" t="n">
@@ -36031,7 +36031,7 @@
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>ਛੀਨਾ ਰੇਤ ਵਾਲਾ</t>
+          <t>ਛੀਨਾ ਰੇਤਵਾਲਾ</t>
         </is>
       </c>
       <c r="D82" s="30" t="n">
@@ -36107,12 +36107,12 @@
       </c>
       <c r="B83" s="34" t="inlineStr">
         <is>
-          <t>Thakkar Sandhu</t>
+          <t>Thakar Sandhu</t>
         </is>
       </c>
       <c r="C83" s="34" t="inlineStr">
         <is>
-          <t>ਠੱਕਰ ਸੰਧੂ</t>
+          <t>ਠਾਕਰ ਸੰਧੂ</t>
         </is>
       </c>
       <c r="D83" s="35" t="n">
@@ -36350,12 +36350,12 @@
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>Jogi Cheema + Chamiyari</t>
+          <t>Jogi Cheema</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>ਜੋਗੀ ਚੀਮਾ + ਚਮਿਆਰੀ</t>
+          <t>ਜੋਗੀ ਚੀਮਾ</t>
         </is>
       </c>
       <c r="D86" s="30" t="n">
@@ -36512,12 +36512,12 @@
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>Balaggan</t>
+          <t>Balagan</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
         <is>
-          <t>ਬਲੱਗਣ</t>
+          <t>ਬਲਾਗਣ</t>
         </is>
       </c>
       <c r="D88" s="30" t="n">
@@ -36755,7 +36755,7 @@
       </c>
       <c r="B91" s="34" t="inlineStr">
         <is>
-          <t>Duluana</t>
+          <t>Duluaana</t>
         </is>
       </c>
       <c r="C91" s="34" t="inlineStr">
@@ -36836,12 +36836,12 @@
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>Sahaipur, Langarkot, Haveli Harni</t>
+          <t>Sahaipur</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>ਸਹਾਈਪੁਰ, ਲੰਗਰਕੋਟ, ਹਵੇਲੀ ਹਾਰਨੀ</t>
+          <t>ਸਹਾਈਪੁਰ</t>
         </is>
       </c>
       <c r="D92" s="30" t="n">
@@ -36917,12 +36917,12 @@
       </c>
       <c r="B93" s="34" t="inlineStr">
         <is>
-          <t>Bhikari Harni, Saidpur Harni, Bhore Harni</t>
+          <t>Bhikhari Harni</t>
         </is>
       </c>
       <c r="C93" s="34" t="inlineStr">
         <is>
-          <t>ਭਿਖਾਰੀ ਹਾਰਨੀ, ਸੈਦਪੁਰ ਹਾਰਨੀ, ਭੋਰੇ ਹਾਰਨੀ</t>
+          <t>ਭਿਖਾਰੀ ਹਾਰਨੀ</t>
         </is>
       </c>
       <c r="D93" s="35" t="n">
@@ -37808,12 +37808,12 @@
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>Chhorian Bangar</t>
+          <t>Chhaurian Bangar</t>
         </is>
       </c>
       <c r="C104" s="28" t="inlineStr">
         <is>
-          <t>ਛੋੜੀਆ ਬਾਂਗਰ</t>
+          <t>ਛੌੜੀਆਂ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D104" s="30" t="n">
@@ -37889,12 +37889,12 @@
       </c>
       <c r="B105" s="34" t="inlineStr">
         <is>
-          <t>Kotli Siania</t>
+          <t>Kotli Sainian</t>
         </is>
       </c>
       <c r="C105" s="34" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸਿਆਣੀਆਂ</t>
+          <t>ਕੋਟਲੀ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D105" s="35" t="n">
@@ -37970,12 +37970,12 @@
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>Kotli Siania</t>
+          <t>Kotli Sainian</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸਿਆਣੀਆਂ</t>
+          <t>ਕੋਟਲੀ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D106" s="30" t="n">
@@ -38132,12 +38132,12 @@
       </c>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>Saidowal Khurd, Bhaini Kaniya, Chakk Abdul</t>
+          <t>Bhaini Kanian</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
         <is>
-          <t>ਸੈਦੋਵਾਲ ਖੁਰਦ, ਭੈਣੀ ਕਾਨੀਆਂ, ਚੱਕ ਅਬਦੁਲ</t>
+          <t>ਭੈਣੀ ਕਾਨੀਆਂ</t>
         </is>
       </c>
       <c r="D108" s="30" t="n">
@@ -38213,12 +38213,12 @@
       </c>
       <c r="B109" s="34" t="inlineStr">
         <is>
-          <t>Darapur, Jangal</t>
+          <t>Darapur</t>
         </is>
       </c>
       <c r="C109" s="34" t="inlineStr">
         <is>
-          <t>ਦਾਰਾਪੁਰ, ਜੰਗਲ</t>
+          <t>ਦਾਰਾਪੁਰ</t>
         </is>
       </c>
       <c r="D109" s="35" t="n">
@@ -38294,12 +38294,12 @@
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>Gulepur, Gargarian</t>
+          <t>Gunopur</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
         <is>
-          <t>ਗੁਲੇਪੁਰ, ਗਾਰਗੜੀਆਂ</t>
+          <t>ਗੁਨੋਪੁਰ</t>
         </is>
       </c>
       <c r="D110" s="30" t="n">
@@ -38375,12 +38375,12 @@
       </c>
       <c r="B111" s="34" t="inlineStr">
         <is>
-          <t>Gulepur</t>
+          <t>Gunopur</t>
         </is>
       </c>
       <c r="C111" s="34" t="inlineStr">
         <is>
-          <t>ਗੁਲੇਪੁਰ</t>
+          <t>ਗੁਨੋਪੁਰ</t>
         </is>
       </c>
       <c r="D111" s="35" t="n">
@@ -38537,12 +38537,12 @@
       </c>
       <c r="B113" s="34" t="inlineStr">
         <is>
-          <t>Jagowal Bet, Jaati Sarai, Bhuriya Gujran</t>
+          <t>Jagowal Bet</t>
         </is>
       </c>
       <c r="C113" s="34" t="inlineStr">
         <is>
-          <t>ਜਾਗੋਵਾਲ ਬੇਟ, ਜਾਤੀ ਸਰਾਏ, ਭੂਰੀਆ ਗੁਜਰਾਂ</t>
+          <t>ਜਾਗੋਵਾਲ ਬੇਟ</t>
         </is>
       </c>
       <c r="D113" s="35" t="n">
@@ -38699,12 +38699,12 @@
       </c>
       <c r="B115" s="34" t="inlineStr">
         <is>
-          <t>Bhaini Paswal, Randhawa Colony</t>
+          <t>Bhaini Paswal</t>
         </is>
       </c>
       <c r="C115" s="34" t="inlineStr">
         <is>
-          <t>ਭੈਣੀ ਪਸਵਾਲ, ਰੰਧਾਵਾ ਕਲੋਨੀ</t>
+          <t>ਭੈਣੀ ਪਸਵਾਲ</t>
         </is>
       </c>
       <c r="D115" s="35" t="n">
@@ -38780,12 +38780,12 @@
       </c>
       <c r="B116" s="28" t="inlineStr">
         <is>
-          <t>Kishanpur, Kathana, Yodhe</t>
+          <t>Kishanpur</t>
         </is>
       </c>
       <c r="C116" s="28" t="inlineStr">
         <is>
-          <t>ਕਿਸ਼ਨਪੁਰ, ਕਠਾਣਾ, ਯੋਧੇ</t>
+          <t>ਕਿਸ਼ਨਪੁਰ</t>
         </is>
       </c>
       <c r="D116" s="30" t="n">
@@ -38861,12 +38861,12 @@
       </c>
       <c r="B117" s="34" t="inlineStr">
         <is>
-          <t>Munan Kalan</t>
+          <t>Munnan Kalan</t>
         </is>
       </c>
       <c r="C117" s="34" t="inlineStr">
         <is>
-          <t>ਮੰਨਣ ਕਲਾਂ</t>
+          <t>ਮੁੰਨਣ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D117" s="35" t="n">
@@ -38942,12 +38942,12 @@
       </c>
       <c r="B118" s="28" t="inlineStr">
         <is>
-          <t>Bujarh</t>
+          <t>Bajar</t>
         </is>
       </c>
       <c r="C118" s="28" t="inlineStr">
         <is>
-          <t>ਬੁਜਾੜ</t>
+          <t>ਬਾਜੜ</t>
         </is>
       </c>
       <c r="D118" s="30" t="n">
@@ -39023,12 +39023,12 @@
       </c>
       <c r="B119" s="34" t="inlineStr">
         <is>
-          <t>Baruhia Molian, Piro Nangal, Sarwarpur, Bhulripur, Bhum</t>
+          <t>Bhurian Sainia</t>
         </is>
       </c>
       <c r="C119" s="34" t="inlineStr">
         <is>
-          <t>ਬਰੂਹੀਆ ਮੋਲੀਆਂ, ਪੀਰੋ ਨੰਗਲ, ਸਰਵਰਪੁਰ, ਭੁਲੜੀਪੁਰ, ਭੂਮ</t>
+          <t>ਭੂਰੀਆਂ ਸੈਣੀਆਂ</t>
         </is>
       </c>
       <c r="D119" s="35" t="n">
@@ -39109,7 +39109,7 @@
       </c>
       <c r="C120" s="28" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਸਰੀਫ</t>
+          <t>ਚੱਕ ਸ਼ਰੀਫ</t>
         </is>
       </c>
       <c r="D120" s="30" t="n">
@@ -39190,7 +39190,7 @@
       </c>
       <c r="C121" s="34" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਸਰੀਫ</t>
+          <t>ਚੱਕ ਸ਼ਰੀਫ</t>
         </is>
       </c>
       <c r="D121" s="35" t="n">
@@ -39266,12 +39266,12 @@
       </c>
       <c r="B122" s="28" t="inlineStr">
         <is>
-          <t>Kotla Gujran, Jhanda Gujran</t>
+          <t>Kotla Gujran</t>
         </is>
       </c>
       <c r="C122" s="28" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਗੁਜਰਾਂ, ਝੰਡਾ ਗੁਜਰਾਂ</t>
+          <t>ਕੋਟਲਾ ਗੁਜਰਾਂ</t>
         </is>
       </c>
       <c r="D122" s="30" t="n">
@@ -39509,12 +39509,12 @@
       </c>
       <c r="B125" s="34" t="inlineStr">
         <is>
-          <t>Kotli Garhwan</t>
+          <t>Kotli Ralwan</t>
         </is>
       </c>
       <c r="C125" s="34" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਗਰਲਵਾਂ</t>
+          <t>ਕੋਟਲੀ ਰਲਵਾਂ</t>
         </is>
       </c>
       <c r="D125" s="35" t="n">
@@ -39590,7 +39590,7 @@
       </c>
       <c r="B126" s="28" t="inlineStr">
         <is>
-          <t>Chak Yakub</t>
+          <t>Chak Yaqub</t>
         </is>
       </c>
       <c r="C126" s="28" t="inlineStr">
@@ -39676,7 +39676,7 @@
       </c>
       <c r="C127" s="34" t="inlineStr">
         <is>
-          <t>ਲਾਧੂਪੁਰ</t>
+          <t>ਲੱਧੂਪੁਰ</t>
         </is>
       </c>
       <c r="D127" s="35" t="n">
@@ -39757,7 +39757,7 @@
       </c>
       <c r="C128" s="28" t="inlineStr">
         <is>
-          <t>ਨੈਨੇਕੋਟ</t>
+          <t>ਨੈਣੇਕੋਟ</t>
         </is>
       </c>
       <c r="D128" s="30" t="n">
@@ -39914,12 +39914,12 @@
       </c>
       <c r="B130" s="28" t="inlineStr">
         <is>
-          <t>Raowal</t>
+          <t>Rauwal</t>
         </is>
       </c>
       <c r="C130" s="28" t="inlineStr">
         <is>
-          <t>ਰਾਓਵਾਲ</t>
+          <t>ਰਾਊਵਾਲ</t>
         </is>
       </c>
       <c r="D130" s="30" t="n">
@@ -40000,7 +40000,7 @@
       </c>
       <c r="C131" s="34" t="inlineStr">
         <is>
-          <t>ਨਿਮਾਣੇ</t>
+          <t>ਨੀਮਾਣੇ</t>
         </is>
       </c>
       <c r="D131" s="35" t="n">
@@ -40157,7 +40157,7 @@
       </c>
       <c r="B133" s="34" t="inlineStr">
         <is>
-          <t>Bhittewadd</t>
+          <t>Bhite Wad</t>
         </is>
       </c>
       <c r="C133" s="34" t="inlineStr">
@@ -40238,7 +40238,7 @@
       </c>
       <c r="B134" s="28" t="inlineStr">
         <is>
-          <t>Kot Todar Mal</t>
+          <t>Kot Todar Mall</t>
         </is>
       </c>
       <c r="C134" s="28" t="inlineStr">
@@ -40319,7 +40319,7 @@
       </c>
       <c r="B135" s="34" t="inlineStr">
         <is>
-          <t>Kot Todar Mal</t>
+          <t>Kot Todar Mall</t>
         </is>
       </c>
       <c r="C135" s="34" t="inlineStr">
@@ -40400,12 +40400,12 @@
       </c>
       <c r="B136" s="28" t="inlineStr">
         <is>
-          <t>Rooda Buttar</t>
+          <t>Rurha Buttar</t>
         </is>
       </c>
       <c r="C136" s="28" t="inlineStr">
         <is>
-          <t>ਰੂੜਾ ਬੁੱਟਰ</t>
+          <t>ਰੂੜ੍ਹਾ ਬੁੱਟਰ</t>
         </is>
       </c>
       <c r="D136" s="30" t="n">
@@ -40481,12 +40481,12 @@
       </c>
       <c r="B137" s="34" t="inlineStr">
         <is>
-          <t>Malian</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="C137" s="34" t="inlineStr">
         <is>
-          <t>ਮਾਲੀਆਂ</t>
+          <t>ਮਾਲੀਆ</t>
         </is>
       </c>
       <c r="D137" s="35" t="n">
@@ -40724,12 +40724,12 @@
       </c>
       <c r="B140" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 4</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C140" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 4</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D140" s="30" t="n">
@@ -40805,12 +40805,12 @@
       </c>
       <c r="B141" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 2</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C141" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 2</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D141" s="35" t="n">
@@ -40886,12 +40886,12 @@
       </c>
       <c r="B142" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 2</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C142" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 2</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D142" s="30" t="n">
@@ -40967,12 +40967,12 @@
       </c>
       <c r="B143" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 1</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C143" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 1</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D143" s="35" t="n">
@@ -41048,12 +41048,12 @@
       </c>
       <c r="B144" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 7</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C144" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 7</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D144" s="30" t="n">
@@ -41129,12 +41129,12 @@
       </c>
       <c r="B145" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 8</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C145" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 8</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D145" s="35" t="n">
@@ -41210,12 +41210,12 @@
       </c>
       <c r="B146" s="28" t="inlineStr">
         <is>
-          <t>Qadian Civil Lines</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C146" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਸਿਵਲ ਲਾਈਨ</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D146" s="30" t="n">
@@ -41291,12 +41291,12 @@
       </c>
       <c r="B147" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 6</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C147" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 6</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D147" s="35" t="n">
@@ -41372,12 +41372,12 @@
       </c>
       <c r="B148" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 5</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C148" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 5</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D148" s="30" t="n">
@@ -41453,12 +41453,12 @@
       </c>
       <c r="B149" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 5</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C149" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 5</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D149" s="35" t="n">
@@ -41534,12 +41534,12 @@
       </c>
       <c r="B150" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 11</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C150" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 11</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D150" s="30" t="n">
@@ -41615,12 +41615,12 @@
       </c>
       <c r="B151" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 10</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C151" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 10</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D151" s="35" t="n">
@@ -41696,12 +41696,12 @@
       </c>
       <c r="B152" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 12</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C152" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 12</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D152" s="30" t="n">
@@ -41777,12 +41777,12 @@
       </c>
       <c r="B153" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 9</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C153" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 9</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D153" s="35" t="n">
@@ -41858,12 +41858,12 @@
       </c>
       <c r="B154" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 13</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C154" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 13</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D154" s="30" t="n">
@@ -41939,12 +41939,12 @@
       </c>
       <c r="B155" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 15</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C155" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 15</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D155" s="35" t="n">
@@ -42020,12 +42020,12 @@
       </c>
       <c r="B156" s="28" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 14</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C156" s="28" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 14</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D156" s="30" t="n">
@@ -42101,12 +42101,12 @@
       </c>
       <c r="B157" s="34" t="inlineStr">
         <is>
-          <t>Qadian Ward No. 3</t>
+          <t>Qadian</t>
         </is>
       </c>
       <c r="C157" s="34" t="inlineStr">
         <is>
-          <t>ਕਾਦੀਆਂ ਵਾਰਡ ਨੰ. 3</t>
+          <t>ਕਾਦੀਆਂ</t>
         </is>
       </c>
       <c r="D157" s="35" t="n">
@@ -42263,12 +42263,12 @@
       </c>
       <c r="B159" s="34" t="inlineStr">
         <is>
-          <t>Bhagatpura Rathwala</t>
+          <t>Patti Bhagtupur</t>
         </is>
       </c>
       <c r="C159" s="34" t="inlineStr">
         <is>
-          <t>ਭਗਤਪੁਰਾ ਰੱਥਵਾਲਾ</t>
+          <t>ਪੱਤੀ ਭਗਤੂਪੁਰ</t>
         </is>
       </c>
       <c r="D159" s="35" t="n">
@@ -42344,12 +42344,12 @@
       </c>
       <c r="B160" s="28" t="inlineStr">
         <is>
-          <t>Nangal Baghbana</t>
+          <t>Nangal Bagbana</t>
         </is>
       </c>
       <c r="C160" s="28" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਬਾਗਬਾਨਾ</t>
+          <t>ਨੰਗਲ ਬਾਗ਼ਬਾਨਾਂ</t>
         </is>
       </c>
       <c r="D160" s="30" t="n">
@@ -42425,7 +42425,7 @@
       </c>
       <c r="B161" s="34" t="inlineStr">
         <is>
-          <t>Chhota Nangal</t>
+          <t>Chota Nangal</t>
         </is>
       </c>
       <c r="C161" s="34" t="inlineStr">
@@ -42506,7 +42506,7 @@
       </c>
       <c r="B162" s="28" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C162" s="28" t="inlineStr">
@@ -42587,7 +42587,7 @@
       </c>
       <c r="B163" s="34" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C163" s="34" t="inlineStr">
@@ -42668,7 +42668,7 @@
       </c>
       <c r="B164" s="28" t="inlineStr">
         <is>
-          <t>Kahlwan</t>
+          <t>Kahalwan</t>
         </is>
       </c>
       <c r="C164" s="28" t="inlineStr">
@@ -42754,7 +42754,7 @@
       </c>
       <c r="C165" s="34" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D165" s="35" t="n">
@@ -42835,7 +42835,7 @@
       </c>
       <c r="C166" s="28" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D166" s="30" t="n">
@@ -42916,7 +42916,7 @@
       </c>
       <c r="C167" s="34" t="inlineStr">
         <is>
-          <t>ਬਸਰਈ</t>
+          <t>ਬਸਰਾਏ</t>
         </is>
       </c>
       <c r="D167" s="35" t="n">
@@ -42992,12 +42992,12 @@
       </c>
       <c r="B168" s="28" t="inlineStr">
         <is>
-          <t>Daili Bangar</t>
+          <t>Bhaini Bangar</t>
         </is>
       </c>
       <c r="C168" s="28" t="inlineStr">
         <is>
-          <t>ਡੈਲੀ ਬਾਂਗਰ</t>
+          <t>ਭੈਣੀ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D168" s="30" t="n">
@@ -43073,12 +43073,12 @@
       </c>
       <c r="B169" s="34" t="inlineStr">
         <is>
-          <t>Daili Bangar</t>
+          <t>Bhaini Banger</t>
         </is>
       </c>
       <c r="C169" s="34" t="inlineStr">
         <is>
-          <t>ਡੈਲੀ ਬਾਂਗਰ</t>
+          <t>ਭੈਣੀ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D169" s="35" t="n">
@@ -43235,12 +43235,12 @@
       </c>
       <c r="B171" s="34" t="inlineStr">
         <is>
-          <t>Salarpur</t>
+          <t>Salahpur</t>
         </is>
       </c>
       <c r="C171" s="34" t="inlineStr">
         <is>
-          <t>ਸਲਾਰਪੁਰ</t>
+          <t>ਸਲਾਹਪੁਰ</t>
         </is>
       </c>
       <c r="D171" s="35" t="n">
@@ -43316,12 +43316,12 @@
       </c>
       <c r="B172" s="28" t="inlineStr">
         <is>
-          <t>Chandogi Mayian Singh</t>
+          <t>Pandori Maiya Singh</t>
         </is>
       </c>
       <c r="C172" s="28" t="inlineStr">
         <is>
-          <t>ਚੰਡੋਗੀ ਮਈਆਂ ਸਿੰਘ</t>
+          <t>ਪੰਡੋਰੀ ਮਈਆਂ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D172" s="30" t="n">
@@ -43402,7 +43402,7 @@
       </c>
       <c r="C173" s="34" t="inlineStr">
         <is>
-          <t>ਕੂੰਟ</t>
+          <t>ਕੁੰਟ</t>
         </is>
       </c>
       <c r="D173" s="35" t="n">
@@ -43483,7 +43483,7 @@
       </c>
       <c r="C174" s="28" t="inlineStr">
         <is>
-          <t>ਗੋਹਤ ਖੁਰਦ</t>
+          <t>ਘੋਟ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D174" s="30" t="n">
@@ -43640,7 +43640,7 @@
       </c>
       <c r="B176" s="28" t="inlineStr">
         <is>
-          <t>Chib</t>
+          <t>Chibb</t>
         </is>
       </c>
       <c r="C176" s="28" t="inlineStr">
@@ -43726,7 +43726,7 @@
       </c>
       <c r="C177" s="34" t="inlineStr">
         <is>
-          <t>ਭੱਟੀਆਂ</t>
+          <t>ਭੱਠੀਆਂ</t>
         </is>
       </c>
       <c r="D177" s="35" t="n">
@@ -43807,7 +43807,7 @@
       </c>
       <c r="C178" s="28" t="inlineStr">
         <is>
-          <t>ਭੱਟੀਆਂ</t>
+          <t>ਭੱਠੀਆਂ</t>
         </is>
       </c>
       <c r="D178" s="30" t="n">
@@ -43883,12 +43883,12 @@
       </c>
       <c r="B179" s="34" t="inlineStr">
         <is>
-          <t>Jangowal Bangar</t>
+          <t>Jagowal Bangar</t>
         </is>
       </c>
       <c r="C179" s="34" t="inlineStr">
         <is>
-          <t>ਜਾਂਗੋਵਾਲ ਬਾਂਗਰ</t>
+          <t>ਜਾਗੋਵਾਲ ਬਾਂਗਰ</t>
         </is>
       </c>
       <c r="D179" s="35" t="n">
@@ -43964,7 +43964,7 @@
       </c>
       <c r="B180" s="28" t="inlineStr">
         <is>
-          <t>Kiri Afghana</t>
+          <t>Kiri Afgana</t>
         </is>
       </c>
       <c r="C180" s="28" t="inlineStr">
@@ -44207,12 +44207,12 @@
       </c>
       <c r="B183" s="34" t="inlineStr">
         <is>
-          <t>Ghukkan</t>
+          <t>Ghookla</t>
         </is>
       </c>
       <c r="C183" s="34" t="inlineStr">
         <is>
-          <t>ਘੁੱਕਲਾਂ</t>
+          <t>ਘੂਕਲਾ</t>
         </is>
       </c>
       <c r="D183" s="35" t="n">
@@ -44531,12 +44531,12 @@
       </c>
       <c r="B187" s="34" t="inlineStr">
         <is>
-          <t>Tugalwal</t>
+          <t>Tugalwala</t>
         </is>
       </c>
       <c r="C187" s="34" t="inlineStr">
         <is>
-          <t>ਤੁਗਲਵਾਲ</t>
+          <t>ਤੁਗਲਵਾਲਾ</t>
         </is>
       </c>
       <c r="D187" s="35" t="n">
@@ -44612,12 +44612,12 @@
       </c>
       <c r="B188" s="28" t="inlineStr">
         <is>
-          <t>Tugalwal</t>
+          <t>Tugalwala</t>
         </is>
       </c>
       <c r="C188" s="28" t="inlineStr">
         <is>
-          <t>ਤੁਗਲਵਾਲ</t>
+          <t>ਤੁਗਲਵਾਲਾ</t>
         </is>
       </c>
       <c r="D188" s="30" t="n">
@@ -44774,12 +44774,12 @@
       </c>
       <c r="B190" s="28" t="inlineStr">
         <is>
-          <t>Seeh Bhatti</t>
+          <t>Shih Bhatti</t>
         </is>
       </c>
       <c r="C190" s="28" t="inlineStr">
         <is>
-          <t>ਸੀਂਹ ਭੱਟੀ</t>
+          <t>ਸ਼ੀਂਹ ਭੱਟੀ</t>
         </is>
       </c>
       <c r="D190" s="30" t="n">
@@ -44855,12 +44855,12 @@
       </c>
       <c r="B191" s="34" t="inlineStr">
         <is>
-          <t>Seeh Bhatti</t>
+          <t>Shihn Bhatti</t>
         </is>
       </c>
       <c r="C191" s="34" t="inlineStr">
         <is>
-          <t>ਸੀਂਹ ਭੱਟੀ</t>
+          <t>ਸ਼ੀਂਹ ਭੱਟੀ</t>
         </is>
       </c>
       <c r="D191" s="35" t="n">
@@ -45098,12 +45098,12 @@
       </c>
       <c r="B194" s="28" t="inlineStr">
         <is>
-          <t>Thakkarwal</t>
+          <t>Thakarwal</t>
         </is>
       </c>
       <c r="C194" s="28" t="inlineStr">
         <is>
-          <t>ਠੱਕਰਵਾਲ</t>
+          <t>ਠਾਕਰਵਾਲ</t>
         </is>
       </c>
       <c r="D194" s="30" t="n">
@@ -45179,12 +45179,12 @@
       </c>
       <c r="B195" s="34" t="inlineStr">
         <is>
-          <t>Sooch</t>
+          <t>Sunch</t>
         </is>
       </c>
       <c r="C195" s="34" t="inlineStr">
         <is>
-          <t>ਸੂਚ</t>
+          <t>ਸੁੰਚ</t>
         </is>
       </c>
       <c r="D195" s="35" t="n">
@@ -45260,12 +45260,12 @@
       </c>
       <c r="B196" s="28" t="inlineStr">
         <is>
-          <t>Datarpur, Bhochna</t>
+          <t>Datarpur</t>
         </is>
       </c>
       <c r="C196" s="28" t="inlineStr">
         <is>
-          <t>ਦਤਾਰਪੁਰ, ਭੋਚਨਾ</t>
+          <t>ਦਤਾਰਪੁਰ</t>
         </is>
       </c>
       <c r="D196" s="30" t="n">
@@ -45422,12 +45422,12 @@
       </c>
       <c r="B198" s="28" t="inlineStr">
         <is>
-          <t>Ferochechi</t>
+          <t>Phero Chechi</t>
         </is>
       </c>
       <c r="C198" s="28" t="inlineStr">
         <is>
-          <t>ਫੇਰੋਚੇਚੀ</t>
+          <t>ਫੇਰੋ ਚੇਚੀ</t>
         </is>
       </c>
       <c r="D198" s="30" t="n">
@@ -45503,12 +45503,12 @@
       </c>
       <c r="B199" s="34" t="inlineStr">
         <is>
-          <t>Jeendarh</t>
+          <t>Jindarh</t>
         </is>
       </c>
       <c r="C199" s="34" t="inlineStr">
         <is>
-          <t>ਜੀਂਦੜ</t>
+          <t>ਜਿੰਦੜ</t>
         </is>
       </c>
       <c r="D199" s="35" t="n">
@@ -45584,7 +45584,7 @@
       </c>
       <c r="B200" s="28" t="inlineStr">
         <is>
-          <t>Ghorewah</t>
+          <t>Ghorhewah</t>
         </is>
       </c>
       <c r="C200" s="28" t="inlineStr">
@@ -45827,12 +45827,12 @@
       </c>
       <c r="B203" s="34" t="inlineStr">
         <is>
-          <t>Mehrey</t>
+          <t>Mehrhe</t>
         </is>
       </c>
       <c r="C203" s="34" t="inlineStr">
         <is>
-          <t>ਮੈਹੜੇ</t>
+          <t>ਮਹਿੜੇ</t>
         </is>
       </c>
       <c r="D203" s="35" t="n">
@@ -46232,12 +46232,12 @@
       </c>
       <c r="B208" s="28" t="inlineStr">
         <is>
-          <t>Dhandoi</t>
+          <t>Balwanda</t>
         </is>
       </c>
       <c r="C208" s="28" t="inlineStr">
         <is>
-          <t>ਧਾਂਦੋਈ</t>
+          <t>ਬਲਵੰਡਾ</t>
         </is>
       </c>
       <c r="D208" s="30" t="n">
@@ -46313,12 +46313,12 @@
       </c>
       <c r="B209" s="34" t="inlineStr">
         <is>
-          <t>Chhichhda</t>
+          <t>Chhichra</t>
         </is>
       </c>
       <c r="C209" s="34" t="inlineStr">
         <is>
-          <t>ਛਿੱਛੜਾ</t>
+          <t>ਛਿੱਛਰਾ</t>
         </is>
       </c>
       <c r="D209" s="35" t="n">
@@ -46394,7 +46394,7 @@
       </c>
       <c r="B210" s="28" t="inlineStr">
         <is>
-          <t>Raju Bela</t>
+          <t>Rajubela</t>
         </is>
       </c>
       <c r="C210" s="28" t="inlineStr">
@@ -46475,7 +46475,7 @@
       </c>
       <c r="B211" s="34" t="inlineStr">
         <is>
-          <t>Alma</t>
+          <t>Aalma</t>
         </is>
       </c>
       <c r="C211" s="34" t="inlineStr">
@@ -46556,12 +46556,12 @@
       </c>
       <c r="B212" s="28" t="inlineStr">
         <is>
-          <t>Awan, Salarpur, Bishanpur, Kisana, Dhore Kalian, Kotli Gujran</t>
+          <t>Awan</t>
         </is>
       </c>
       <c r="C212" s="28" t="inlineStr">
         <is>
-          <t>ਅਵਾਣ, ਸਲਾਰਪੁਰ, ਬਿਸਨਪੁਰ, ਕਿਸਾਨਾ, ਧੋਰੇ ਕਲੀਆਂ, ਕੋਟਲੀ ਗੁਜਰਾਂ</t>
+          <t>ਅਵਾਣ</t>
         </is>
       </c>
       <c r="D212" s="30" t="n">
@@ -46718,12 +46718,12 @@
       </c>
       <c r="B214" s="28" t="inlineStr">
         <is>
-          <t>Navian Bagrian, Mitha</t>
+          <t>Nawian Bagrhian</t>
         </is>
       </c>
       <c r="C214" s="28" t="inlineStr">
         <is>
-          <t>ਨਵੀਆਂ ਬਗੜੀਆਂ, ਮਿਠਾ</t>
+          <t>ਨਵੀਆਂ ਬਾਗੜੀਆਂ</t>
         </is>
       </c>
       <c r="D214" s="30" t="n">
@@ -46799,12 +46799,12 @@
       </c>
       <c r="B215" s="34" t="inlineStr">
         <is>
-          <t>Bagrian</t>
+          <t>Bagrhia</t>
         </is>
       </c>
       <c r="C215" s="34" t="inlineStr">
         <is>
-          <t>ਬਾਗੜੀਆਂ</t>
+          <t>ਬਾਗੜੀਆ</t>
         </is>
       </c>
       <c r="D215" s="35" t="n">
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B216" s="28" t="inlineStr">
         <is>
-          <t>Bagrian</t>
+          <t>Bagrhia</t>
         </is>
       </c>
       <c r="C216" s="28" t="inlineStr">
         <is>
-          <t>ਬਾਗੜੀਆਂ</t>
+          <t>ਬਾਗੜੀਆ</t>
         </is>
       </c>
       <c r="D216" s="30" t="n">
@@ -47123,12 +47123,12 @@
       </c>
       <c r="B219" s="34" t="inlineStr">
         <is>
-          <t>Mullanwal</t>
+          <t>Mulanwal</t>
         </is>
       </c>
       <c r="C219" s="34" t="inlineStr">
         <is>
-          <t>ਮੁੱਲਾਂਵਾਲ</t>
+          <t>ਮੁਲਾਂਵਾਲ</t>
         </is>
       </c>
       <c r="D219" s="35" t="n">
@@ -47447,12 +47447,12 @@
       </c>
       <c r="B223" s="34" t="inlineStr">
         <is>
-          <t>Munnan, Ghulla Thatha</t>
+          <t>Munnan</t>
         </is>
       </c>
       <c r="C223" s="34" t="inlineStr">
         <is>
-          <t>ਮੁੰਨਣ, ਘੁੱਲਾ ਥਾਥਾ</t>
+          <t>ਮੁੰਨਣ</t>
         </is>
       </c>
       <c r="D223" s="35" t="n">
